--- a/research/traditional_assets/database/data/ghana/ghana_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1587997630207021</v>
+        <v>0.1584365136131504</v>
       </c>
       <c r="C2">
-        <v>130.1064837529739</v>
+        <v>129.1711915589176</v>
       </c>
       <c r="D2">
-        <v>104.4064837529739</v>
+        <v>104.7431915589176</v>
       </c>
       <c r="E2">
-        <v>-12</v>
+        <v>-10.728</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.272</v>
       </c>
       <c r="G2">
         <v>25.7</v>
@@ -1451,28 +1451,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0639816</v>
       </c>
       <c r="N2">
-        <v>9.460000000000001</v>
+        <v>9.396018400000001</v>
       </c>
       <c r="O2">
-        <v>2.365</v>
+        <v>2.3490046</v>
       </c>
       <c r="P2">
-        <v>7.095000000000001</v>
+        <v>7.0470138</v>
       </c>
       <c r="Q2">
-        <v>13.885</v>
+        <v>13.8370138</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1587997630207021</v>
+        <v>0.159655821831465</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6963280330109818</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>147.8550083148905</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1584365136131504</v>
+        <v>0.1580732642055986</v>
       </c>
       <c r="C3">
-        <v>129.1711915589176</v>
+        <v>128.2380781366623</v>
       </c>
       <c r="D3">
-        <v>104.7431915589176</v>
+        <v>105.0820781366623</v>
       </c>
       <c r="E3">
-        <v>-10.728</v>
+        <v>-9.456</v>
       </c>
       <c r="F3">
-        <v>1.272</v>
+        <v>2.544</v>
       </c>
       <c r="G3">
         <v>25.7</v>
@@ -1533,28 +1533,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0639816</v>
+        <v>0.1279632</v>
       </c>
       <c r="N3">
-        <v>9.396018400000001</v>
+        <v>9.332036800000001</v>
       </c>
       <c r="O3">
-        <v>2.3490046</v>
+        <v>2.3330092</v>
       </c>
       <c r="P3">
-        <v>7.0470138</v>
+        <v>6.999027600000001</v>
       </c>
       <c r="Q3">
-        <v>13.8370138</v>
+        <v>13.7890276</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.159655821831465</v>
+        <v>0.1605293512302027</v>
       </c>
       <c r="T3">
-        <v>0.6963280330109818</v>
+        <v>0.7016704300725976</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>147.8550083148905</v>
+        <v>73.92750415744527</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1580732642055986</v>
+        <v>0.1577100147980469</v>
       </c>
       <c r="C4">
-        <v>128.2380781366623</v>
+        <v>127.3071647024744</v>
       </c>
       <c r="D4">
-        <v>105.0820781366623</v>
+        <v>105.4231647024744</v>
       </c>
       <c r="E4">
-        <v>-9.456</v>
+        <v>-8.184000000000001</v>
       </c>
       <c r="F4">
-        <v>2.544</v>
+        <v>3.816</v>
       </c>
       <c r="G4">
         <v>25.7</v>
@@ -1615,28 +1615,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M4">
-        <v>0.1279632</v>
+        <v>0.1919448</v>
       </c>
       <c r="N4">
-        <v>9.332036800000001</v>
+        <v>9.268055200000001</v>
       </c>
       <c r="O4">
-        <v>2.3330092</v>
+        <v>2.3170138</v>
       </c>
       <c r="P4">
-        <v>6.999027600000001</v>
+        <v>6.951041400000001</v>
       </c>
       <c r="Q4">
-        <v>13.7890276</v>
+        <v>13.7410414</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1605293512302027</v>
+        <v>0.1614208915443782</v>
       </c>
       <c r="T4">
-        <v>0.7016704300725976</v>
+        <v>0.7071229796509474</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.92750415744527</v>
+        <v>49.28500277163019</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1577100147980469</v>
+        <v>0.1573467653904951</v>
       </c>
       <c r="C5">
-        <v>127.3071647024744</v>
+        <v>126.3784727489816</v>
       </c>
       <c r="D5">
-        <v>105.4231647024744</v>
+        <v>105.7664727489816</v>
       </c>
       <c r="E5">
-        <v>-8.184000000000001</v>
+        <v>-6.912</v>
       </c>
       <c r="F5">
-        <v>3.816</v>
+        <v>5.088</v>
       </c>
       <c r="G5">
         <v>25.7</v>
@@ -1697,28 +1697,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M5">
-        <v>0.1919448</v>
+        <v>0.2559264</v>
       </c>
       <c r="N5">
-        <v>9.268055200000001</v>
+        <v>9.204073600000001</v>
       </c>
       <c r="O5">
-        <v>2.3170138</v>
+        <v>2.3010184</v>
       </c>
       <c r="P5">
-        <v>6.951041400000001</v>
+        <v>6.903055200000001</v>
       </c>
       <c r="Q5">
-        <v>13.7410414</v>
+        <v>13.6930552</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1614208915443782</v>
+        <v>0.1623310056150991</v>
       </c>
       <c r="T5">
-        <v>0.7071229796509474</v>
+        <v>0.7126891240121798</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.28500277163019</v>
+        <v>36.96375207872264</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1573467653904951</v>
+        <v>0.1569835159829434</v>
       </c>
       <c r="C6">
-        <v>126.3784727489816</v>
+        <v>125.452024049687</v>
       </c>
       <c r="D6">
-        <v>105.7664727489816</v>
+        <v>106.112024049687</v>
       </c>
       <c r="E6">
-        <v>-6.912</v>
+        <v>-5.64</v>
       </c>
       <c r="F6">
-        <v>5.088</v>
+        <v>6.36</v>
       </c>
       <c r="G6">
         <v>25.7</v>
@@ -1779,28 +1779,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M6">
-        <v>0.2559264</v>
+        <v>0.319908</v>
       </c>
       <c r="N6">
-        <v>9.204073600000001</v>
+        <v>9.140092000000001</v>
       </c>
       <c r="O6">
-        <v>2.3010184</v>
+        <v>2.285023</v>
       </c>
       <c r="P6">
-        <v>6.903055200000001</v>
+        <v>6.855069</v>
       </c>
       <c r="Q6">
-        <v>13.6930552</v>
+        <v>13.645069</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1623310056150991</v>
+        <v>0.1632602799820456</v>
       </c>
       <c r="T6">
-        <v>0.7126891240121798</v>
+        <v>0.7183724503599642</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.96375207872264</v>
+        <v>29.57100166297811</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1569835159829434</v>
+        <v>0.1566202665753916</v>
       </c>
       <c r="C7">
-        <v>125.452024049687</v>
+        <v>124.5278406635727</v>
       </c>
       <c r="D7">
-        <v>106.112024049687</v>
+        <v>106.4598406635727</v>
       </c>
       <c r="E7">
-        <v>-5.64</v>
+        <v>-4.367999999999999</v>
       </c>
       <c r="F7">
-        <v>6.36</v>
+        <v>7.632000000000001</v>
       </c>
       <c r="G7">
         <v>25.7</v>
@@ -1861,28 +1861,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M7">
-        <v>0.319908</v>
+        <v>0.3838896</v>
       </c>
       <c r="N7">
-        <v>9.140092000000001</v>
+        <v>9.076110400000001</v>
       </c>
       <c r="O7">
-        <v>2.285023</v>
+        <v>2.2690276</v>
       </c>
       <c r="P7">
-        <v>6.855069</v>
+        <v>6.807082800000001</v>
       </c>
       <c r="Q7">
-        <v>13.645069</v>
+        <v>13.5970828</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1632602799820456</v>
+        <v>0.1642093261440336</v>
       </c>
       <c r="T7">
-        <v>0.7183724503599642</v>
+        <v>0.7241766985449357</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.57100166297811</v>
+        <v>24.64250138581509</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1566202665753916</v>
+        <v>0.1562570171678399</v>
       </c>
       <c r="C8">
-        <v>124.5278406635727</v>
+        <v>123.6059449397939</v>
       </c>
       <c r="D8">
-        <v>106.4598406635727</v>
+        <v>106.8099449397939</v>
       </c>
       <c r="E8">
-        <v>-4.368</v>
+        <v>-3.096</v>
       </c>
       <c r="F8">
-        <v>7.632</v>
+        <v>8.904</v>
       </c>
       <c r="G8">
         <v>25.7</v>
@@ -1943,28 +1943,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M8">
-        <v>0.3838895999999999</v>
+        <v>0.4478712</v>
       </c>
       <c r="N8">
-        <v>9.076110400000001</v>
+        <v>9.012128800000001</v>
       </c>
       <c r="O8">
-        <v>2.2690276</v>
+        <v>2.2530322</v>
       </c>
       <c r="P8">
-        <v>6.807082800000001</v>
+        <v>6.759096600000001</v>
       </c>
       <c r="Q8">
-        <v>13.5970828</v>
+        <v>13.5490966</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1642093261440336</v>
+        <v>0.1651787819009031</v>
       </c>
       <c r="T8">
-        <v>0.7241766985449357</v>
+        <v>0.7301057692715194</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.64250138581509</v>
+        <v>21.12214404498437</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1562570171678399</v>
+        <v>0.1558937677602881</v>
       </c>
       <c r="C9">
-        <v>123.6059449397939</v>
+        <v>122.6863595224657</v>
       </c>
       <c r="D9">
-        <v>106.8099449397939</v>
+        <v>107.1623595224657</v>
       </c>
       <c r="E9">
-        <v>-3.095999999999998</v>
+        <v>-1.824</v>
       </c>
       <c r="F9">
-        <v>8.904000000000002</v>
+        <v>10.176</v>
       </c>
       <c r="G9">
         <v>25.7</v>
@@ -2025,28 +2025,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M9">
-        <v>0.4478712000000001</v>
+        <v>0.5118528</v>
       </c>
       <c r="N9">
-        <v>9.012128800000001</v>
+        <v>8.948147200000001</v>
       </c>
       <c r="O9">
-        <v>2.2530322</v>
+        <v>2.2370368</v>
       </c>
       <c r="P9">
-        <v>6.759096600000001</v>
+        <v>6.711110400000001</v>
       </c>
       <c r="Q9">
-        <v>13.5490966</v>
+        <v>13.5011104</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1651787819009031</v>
+        <v>0.1661693127829219</v>
       </c>
       <c r="T9">
-        <v>0.7301057692715194</v>
+        <v>0.7361637328399854</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.12214404498436</v>
+        <v>18.48187603936132</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1558937677602881</v>
+        <v>0.1555305183527363</v>
       </c>
       <c r="C10">
-        <v>122.6863595224657</v>
+        <v>121.7691073555458</v>
       </c>
       <c r="D10">
-        <v>107.1623595224657</v>
+        <v>107.5171073555458</v>
       </c>
       <c r="E10">
-        <v>-1.824</v>
+        <v>-0.5519999999999996</v>
       </c>
       <c r="F10">
-        <v>10.176</v>
+        <v>11.448</v>
       </c>
       <c r="G10">
         <v>25.7</v>
@@ -2107,28 +2107,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M10">
-        <v>0.5118528</v>
+        <v>0.5758344</v>
       </c>
       <c r="N10">
-        <v>8.948147200000001</v>
+        <v>8.884165600000001</v>
       </c>
       <c r="O10">
-        <v>2.2370368</v>
+        <v>2.2210414</v>
       </c>
       <c r="P10">
-        <v>6.711110400000001</v>
+        <v>6.6631242</v>
       </c>
       <c r="Q10">
-        <v>13.5011104</v>
+        <v>13.4531242</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1661693127829219</v>
+        <v>0.1671816135744355</v>
       </c>
       <c r="T10">
-        <v>0.7361637328399854</v>
+        <v>0.7423548384649011</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.48187603936132</v>
+        <v>16.42833425721006</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1555305183527363</v>
+        <v>0.1551672689451846</v>
       </c>
       <c r="C11">
-        <v>121.7691073555458</v>
+        <v>120.8542116878132</v>
       </c>
       <c r="D11">
-        <v>107.5171073555458</v>
+        <v>107.8742116878132</v>
       </c>
       <c r="E11">
-        <v>-0.5519999999999996</v>
+        <v>0.7199999999999989</v>
       </c>
       <c r="F11">
-        <v>11.448</v>
+        <v>12.72</v>
       </c>
       <c r="G11">
         <v>25.7</v>
@@ -2189,28 +2189,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M11">
-        <v>0.5758344</v>
+        <v>0.6398159999999999</v>
       </c>
       <c r="N11">
-        <v>8.884165600000001</v>
+        <v>8.820184000000001</v>
       </c>
       <c r="O11">
-        <v>2.2210414</v>
+        <v>2.205046</v>
       </c>
       <c r="P11">
-        <v>6.6631242</v>
+        <v>6.615138000000001</v>
       </c>
       <c r="Q11">
-        <v>13.4531242</v>
+        <v>13.405138</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1671816135744355</v>
+        <v>0.168216409939094</v>
       </c>
       <c r="T11">
-        <v>0.7423548384649011</v>
+        <v>0.748683524214815</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.42833425721006</v>
+        <v>14.78550083148906</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1551672689451846</v>
+        <v>0.1548040195376328</v>
       </c>
       <c r="C12">
-        <v>120.8542116878132</v>
+        <v>119.9416960779479</v>
       </c>
       <c r="D12">
-        <v>107.8742116878132</v>
+        <v>108.2336960779479</v>
       </c>
       <c r="E12">
-        <v>0.7200000000000006</v>
+        <v>1.992000000000001</v>
       </c>
       <c r="F12">
-        <v>12.72</v>
+        <v>13.992</v>
       </c>
       <c r="G12">
         <v>25.7</v>
@@ -2271,28 +2271,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M12">
-        <v>0.6398160000000001</v>
+        <v>0.7037976</v>
       </c>
       <c r="N12">
-        <v>8.820184000000001</v>
+        <v>8.756202400000001</v>
       </c>
       <c r="O12">
-        <v>2.205046</v>
+        <v>2.1890506</v>
       </c>
       <c r="P12">
-        <v>6.615138000000001</v>
+        <v>6.567151800000001</v>
       </c>
       <c r="Q12">
-        <v>13.405138</v>
+        <v>13.3571518</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.168216409939094</v>
+        <v>0.1692744601546436</v>
       </c>
       <c r="T12">
-        <v>0.748683524214815</v>
+        <v>0.7551544276220304</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.78550083148905</v>
+        <v>13.44136439226278</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1548040195376328</v>
+        <v>0.1545757701300811</v>
       </c>
       <c r="C13">
-        <v>119.9416960779479</v>
+        <v>118.896808025557</v>
       </c>
       <c r="D13">
-        <v>108.2336960779479</v>
+        <v>108.460808025557</v>
       </c>
       <c r="E13">
-        <v>1.992000000000001</v>
+        <v>3.263999999999999</v>
       </c>
       <c r="F13">
-        <v>13.992</v>
+        <v>15.264</v>
       </c>
       <c r="G13">
         <v>25.7</v>
@@ -2353,45 +2353,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M13">
-        <v>0.7037976</v>
+        <v>0.7906751999999999</v>
       </c>
       <c r="N13">
-        <v>8.756202400000001</v>
+        <v>8.669324800000002</v>
       </c>
       <c r="O13">
-        <v>2.1890506</v>
+        <v>2.1673312</v>
       </c>
       <c r="P13">
-        <v>6.567151800000001</v>
+        <v>6.501993600000001</v>
       </c>
       <c r="Q13">
-        <v>13.3571518</v>
+        <v>13.2919936</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1692744601546436</v>
+        <v>0.1703565569660012</v>
       </c>
       <c r="T13">
-        <v>0.7551544276220304</v>
+        <v>0.7617723970157734</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.44136439226278</v>
+        <v>11.9644577191747</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1545757701300811</v>
+        <v>0.1542237707225293</v>
       </c>
       <c r="C14">
-        <v>118.896808025557</v>
+        <v>117.9769276752719</v>
       </c>
       <c r="D14">
-        <v>108.460808025557</v>
+        <v>108.8129276752719</v>
       </c>
       <c r="E14">
-        <v>3.263999999999999</v>
+        <v>4.536000000000001</v>
       </c>
       <c r="F14">
-        <v>15.264</v>
+        <v>16.536</v>
       </c>
       <c r="G14">
         <v>25.7</v>
@@ -2435,28 +2435,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M14">
-        <v>0.7906751999999999</v>
+        <v>0.8565648</v>
       </c>
       <c r="N14">
-        <v>8.669324800000002</v>
+        <v>8.603435200000002</v>
       </c>
       <c r="O14">
-        <v>2.1673312</v>
+        <v>2.1508588</v>
       </c>
       <c r="P14">
-        <v>6.501993600000001</v>
+        <v>6.452576400000002</v>
       </c>
       <c r="Q14">
-        <v>13.2919936</v>
+        <v>13.2425764</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1703565569660012</v>
+        <v>0.1714635295661256</v>
       </c>
       <c r="T14">
-        <v>0.7617723970157734</v>
+        <v>0.7685425036369586</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.9644577191747</v>
+        <v>11.04411481769973</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1542237707225293</v>
+        <v>0.1538717713149776</v>
       </c>
       <c r="C15">
-        <v>117.9769276752719</v>
+        <v>117.0593410952577</v>
       </c>
       <c r="D15">
-        <v>108.8129276752719</v>
+        <v>109.1673410952577</v>
       </c>
       <c r="E15">
-        <v>4.536000000000001</v>
+        <v>5.808000000000003</v>
       </c>
       <c r="F15">
-        <v>16.536</v>
+        <v>17.808</v>
       </c>
       <c r="G15">
         <v>25.7</v>
@@ -2517,28 +2517,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M15">
-        <v>0.8565648</v>
+        <v>0.9224544000000001</v>
       </c>
       <c r="N15">
-        <v>8.603435200000002</v>
+        <v>8.537545600000001</v>
       </c>
       <c r="O15">
-        <v>2.1508588</v>
+        <v>2.1343864</v>
       </c>
       <c r="P15">
-        <v>6.452576400000002</v>
+        <v>6.403159200000001</v>
       </c>
       <c r="Q15">
-        <v>13.2425764</v>
+        <v>13.1931592</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1714635295661256</v>
+        <v>0.1725962457150902</v>
       </c>
       <c r="T15">
-        <v>0.7685425036369586</v>
+        <v>0.7754700545981716</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.04411481769973</v>
+        <v>10.25524947357832</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1538717713149776</v>
+        <v>0.1537110219074258</v>
       </c>
       <c r="C16">
-        <v>117.0593410952577</v>
+        <v>115.9499619758209</v>
       </c>
       <c r="D16">
-        <v>109.1673410952577</v>
+        <v>109.3299619758209</v>
       </c>
       <c r="E16">
-        <v>5.808000000000003</v>
+        <v>7.080000000000002</v>
       </c>
       <c r="F16">
-        <v>17.808</v>
+        <v>19.08</v>
       </c>
       <c r="G16">
         <v>25.7</v>
@@ -2599,45 +2599,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M16">
-        <v>0.9224544000000001</v>
+        <v>1.02078</v>
       </c>
       <c r="N16">
-        <v>8.537545600000001</v>
+        <v>8.439220000000001</v>
       </c>
       <c r="O16">
-        <v>2.1343864</v>
+        <v>2.109805</v>
       </c>
       <c r="P16">
-        <v>6.403159200000001</v>
+        <v>6.329415000000001</v>
       </c>
       <c r="Q16">
-        <v>13.1931592</v>
+        <v>13.119415</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1725962457150902</v>
+        <v>0.1737556140087363</v>
       </c>
       <c r="T16">
-        <v>0.7754700545981716</v>
+        <v>0.7825606067584718</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.25524947357832</v>
+        <v>9.267422951076629</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1537110219074258</v>
+        <v>0.153371772499874</v>
       </c>
       <c r="C17">
-        <v>115.9499619758209</v>
+        <v>115.0227561905672</v>
       </c>
       <c r="D17">
-        <v>109.3299619758209</v>
+        <v>109.6747561905672</v>
       </c>
       <c r="E17">
-        <v>7.079999999999998</v>
+        <v>8.352</v>
       </c>
       <c r="F17">
-        <v>19.08</v>
+        <v>20.352</v>
       </c>
       <c r="G17">
         <v>25.7</v>
@@ -2681,28 +2681,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M17">
-        <v>1.02078</v>
+        <v>1.088832</v>
       </c>
       <c r="N17">
-        <v>8.439220000000001</v>
+        <v>8.371168000000001</v>
       </c>
       <c r="O17">
-        <v>2.109805</v>
+        <v>2.092792</v>
       </c>
       <c r="P17">
-        <v>6.329415000000001</v>
+        <v>6.278376000000001</v>
       </c>
       <c r="Q17">
-        <v>13.119415</v>
+        <v>13.068376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1737556140087363</v>
+        <v>0.1749425863093739</v>
       </c>
       <c r="T17">
-        <v>0.7825606067584718</v>
+        <v>0.7898199815892554</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.267422951076631</v>
+        <v>8.688209016634339</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.153371772499874</v>
+        <v>0.1530325230923223</v>
       </c>
       <c r="C18">
-        <v>115.0227561905672</v>
+        <v>114.0977320425575</v>
       </c>
       <c r="D18">
-        <v>109.6747561905672</v>
+        <v>110.0217320425575</v>
       </c>
       <c r="E18">
-        <v>8.352</v>
+        <v>9.624000000000002</v>
       </c>
       <c r="F18">
-        <v>20.352</v>
+        <v>21.624</v>
       </c>
       <c r="G18">
         <v>25.7</v>
@@ -2763,28 +2763,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M18">
-        <v>1.088832</v>
+        <v>1.156884</v>
       </c>
       <c r="N18">
-        <v>8.371168000000001</v>
+        <v>8.303116000000001</v>
       </c>
       <c r="O18">
-        <v>2.092792</v>
+        <v>2.075779</v>
       </c>
       <c r="P18">
-        <v>6.278376000000001</v>
+        <v>6.227337</v>
       </c>
       <c r="Q18">
-        <v>13.068376</v>
+        <v>13.017337</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1749425863093739</v>
+        <v>0.1761581603521956</v>
       </c>
       <c r="T18">
-        <v>0.7898199815892554</v>
+        <v>0.7972542811147568</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.688209016634339</v>
+        <v>8.177137898008791</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1530325230923223</v>
+        <v>0.1526932736847705</v>
       </c>
       <c r="C19">
-        <v>114.0977320425575</v>
+        <v>113.1749103035146</v>
       </c>
       <c r="D19">
-        <v>110.0217320425575</v>
+        <v>110.3709103035146</v>
       </c>
       <c r="E19">
-        <v>9.624000000000002</v>
+        <v>10.896</v>
       </c>
       <c r="F19">
-        <v>21.624</v>
+        <v>22.896</v>
       </c>
       <c r="G19">
         <v>25.7</v>
@@ -2845,28 +2845,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M19">
-        <v>1.156884</v>
+        <v>1.224936</v>
       </c>
       <c r="N19">
-        <v>8.303116000000001</v>
+        <v>8.235064000000001</v>
       </c>
       <c r="O19">
-        <v>2.075779</v>
+        <v>2.058766</v>
       </c>
       <c r="P19">
-        <v>6.227337</v>
+        <v>6.176298000000001</v>
       </c>
       <c r="Q19">
-        <v>13.017337</v>
+        <v>12.966298</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1761581603521956</v>
+        <v>0.1774033825424031</v>
       </c>
       <c r="T19">
-        <v>0.7972542811147568</v>
+        <v>0.8048699050189287</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.177137898008791</v>
+        <v>7.722852459230523</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1526932736847705</v>
+        <v>0.1524680242772188</v>
       </c>
       <c r="C20">
-        <v>113.1749103035146</v>
+        <v>112.1359790448292</v>
       </c>
       <c r="D20">
-        <v>110.3709103035146</v>
+        <v>110.6039790448292</v>
       </c>
       <c r="E20">
-        <v>10.896</v>
+        <v>12.168</v>
       </c>
       <c r="F20">
-        <v>22.896</v>
+        <v>24.168</v>
       </c>
       <c r="G20">
         <v>25.7</v>
@@ -2927,45 +2927,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M20">
-        <v>1.224936</v>
+        <v>1.3123224</v>
       </c>
       <c r="N20">
-        <v>8.235064000000001</v>
+        <v>8.147677600000002</v>
       </c>
       <c r="O20">
-        <v>2.058766</v>
+        <v>2.0369194</v>
       </c>
       <c r="P20">
-        <v>6.176298000000001</v>
+        <v>6.110758200000001</v>
       </c>
       <c r="Q20">
-        <v>12.966298</v>
+        <v>12.9007582</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1774033825424031</v>
+        <v>0.1786793509595294</v>
       </c>
       <c r="T20">
-        <v>0.8048699050189287</v>
+        <v>0.8126735690195002</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.722852459230524</v>
+        <v>7.208594473431226</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1524680242772188</v>
+        <v>0.152134774869667</v>
       </c>
       <c r="C21">
-        <v>112.1359790448292</v>
+        <v>111.2106079866287</v>
       </c>
       <c r="D21">
-        <v>110.6039790448292</v>
+        <v>110.9506079866287</v>
       </c>
       <c r="E21">
-        <v>12.168</v>
+        <v>13.44</v>
       </c>
       <c r="F21">
-        <v>24.168</v>
+        <v>25.44</v>
       </c>
       <c r="G21">
         <v>25.7</v>
@@ -3009,28 +3009,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M21">
-        <v>1.3123224</v>
+        <v>1.381392</v>
       </c>
       <c r="N21">
-        <v>8.147677600000002</v>
+        <v>8.078608000000001</v>
       </c>
       <c r="O21">
-        <v>2.0369194</v>
+        <v>2.019652</v>
       </c>
       <c r="P21">
-        <v>6.110758200000001</v>
+        <v>6.058956</v>
       </c>
       <c r="Q21">
-        <v>12.9007582</v>
+        <v>12.848956</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1786793509595294</v>
+        <v>0.1799872185870838</v>
       </c>
       <c r="T21">
-        <v>0.8126735690195002</v>
+        <v>0.8206723246200858</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.208594473431226</v>
+        <v>6.848164749759663</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.152134774869667</v>
+        <v>0.1518015254621153</v>
       </c>
       <c r="C22">
-        <v>111.2106079866287</v>
+        <v>110.2874164044119</v>
       </c>
       <c r="D22">
-        <v>110.9506079866287</v>
+        <v>111.2994164044119</v>
       </c>
       <c r="E22">
-        <v>13.44</v>
+        <v>14.712</v>
       </c>
       <c r="F22">
-        <v>25.44</v>
+        <v>26.712</v>
       </c>
       <c r="G22">
         <v>25.7</v>
@@ -3091,28 +3091,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M22">
-        <v>1.381392</v>
+        <v>1.4504616</v>
       </c>
       <c r="N22">
-        <v>8.078608000000001</v>
+        <v>8.0095384</v>
       </c>
       <c r="O22">
-        <v>2.019652</v>
+        <v>2.0023846</v>
       </c>
       <c r="P22">
-        <v>6.058956</v>
+        <v>6.0071538</v>
       </c>
       <c r="Q22">
-        <v>12.848956</v>
+        <v>12.7971538</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1799872185870838</v>
+        <v>0.1813281967874877</v>
       </c>
       <c r="T22">
-        <v>0.8206723246200858</v>
+        <v>0.8288735803624583</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.848164749759663</v>
+        <v>6.522061666437773</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1518015254621153</v>
+        <v>0.1514682760545635</v>
       </c>
       <c r="C23">
-        <v>110.2874164044119</v>
+        <v>109.3664249186274</v>
       </c>
       <c r="D23">
-        <v>111.2994164044119</v>
+        <v>111.6504249186275</v>
       </c>
       <c r="E23">
-        <v>14.712</v>
+        <v>15.984</v>
       </c>
       <c r="F23">
-        <v>26.712</v>
+        <v>27.984</v>
       </c>
       <c r="G23">
         <v>25.7</v>
@@ -3173,28 +3173,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M23">
-        <v>1.4504616</v>
+        <v>1.5195312</v>
       </c>
       <c r="N23">
-        <v>8.0095384</v>
+        <v>7.940468800000001</v>
       </c>
       <c r="O23">
-        <v>2.0023846</v>
+        <v>1.9851172</v>
       </c>
       <c r="P23">
-        <v>6.0071538</v>
+        <v>5.9553516</v>
       </c>
       <c r="Q23">
-        <v>12.7971538</v>
+        <v>12.7453516</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1813281967874877</v>
+        <v>0.1827035590443122</v>
       </c>
       <c r="T23">
-        <v>0.8288735803624583</v>
+        <v>0.8372851247136097</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.522061666437774</v>
+        <v>6.22560431796333</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1514682760545635</v>
+        <v>0.1513075266470118</v>
       </c>
       <c r="C24">
-        <v>109.3664249186274</v>
+        <v>108.2645335376894</v>
       </c>
       <c r="D24">
-        <v>111.6504249186275</v>
+        <v>111.8205335376894</v>
       </c>
       <c r="E24">
-        <v>15.984</v>
+        <v>17.256</v>
       </c>
       <c r="F24">
-        <v>27.984</v>
+        <v>29.256</v>
       </c>
       <c r="G24">
         <v>25.7</v>
@@ -3255,45 +3255,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M24">
-        <v>1.5195312</v>
+        <v>1.6178568</v>
       </c>
       <c r="N24">
-        <v>7.940468800000001</v>
+        <v>7.842143200000001</v>
       </c>
       <c r="O24">
-        <v>1.9851172</v>
+        <v>1.9605358</v>
       </c>
       <c r="P24">
-        <v>5.9553516</v>
+        <v>5.8816074</v>
       </c>
       <c r="Q24">
-        <v>12.7453516</v>
+        <v>12.6716074</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1827035590443122</v>
+        <v>0.1841146449961192</v>
       </c>
       <c r="T24">
-        <v>0.8372851247136097</v>
+        <v>0.8459151507362196</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.22560431796333</v>
+        <v>5.847241857252138</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1513075266470118</v>
+        <v>0.15098177723946</v>
       </c>
       <c r="C25">
-        <v>108.2645335376894</v>
+        <v>107.3388432646025</v>
       </c>
       <c r="D25">
-        <v>111.8205335376894</v>
+        <v>112.1668432646025</v>
       </c>
       <c r="E25">
-        <v>17.256</v>
+        <v>18.528</v>
       </c>
       <c r="F25">
-        <v>29.256</v>
+        <v>30.528</v>
       </c>
       <c r="G25">
         <v>25.7</v>
@@ -3337,28 +3337,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M25">
-        <v>1.6178568</v>
+        <v>1.6881984</v>
       </c>
       <c r="N25">
-        <v>7.842143200000001</v>
+        <v>7.771801600000001</v>
       </c>
       <c r="O25">
-        <v>1.9605358</v>
+        <v>1.9429504</v>
       </c>
       <c r="P25">
-        <v>5.8816074</v>
+        <v>5.828851200000001</v>
       </c>
       <c r="Q25">
-        <v>12.6716074</v>
+        <v>12.6188512</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1841146449961192</v>
+        <v>0.1855628647887632</v>
       </c>
       <c r="T25">
-        <v>0.8459151507362196</v>
+        <v>0.854772282706793</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.847241857252138</v>
+        <v>5.603606779866632</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.15098177723946</v>
+        <v>0.1506560278319083</v>
       </c>
       <c r="C26">
-        <v>107.3388432646025</v>
+        <v>106.4153047073625</v>
       </c>
       <c r="D26">
-        <v>112.1668432646025</v>
+        <v>112.5153047073625</v>
       </c>
       <c r="E26">
-        <v>18.528</v>
+        <v>19.8</v>
       </c>
       <c r="F26">
-        <v>30.528</v>
+        <v>31.8</v>
       </c>
       <c r="G26">
         <v>25.7</v>
@@ -3419,28 +3419,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M26">
-        <v>1.6881984</v>
+        <v>1.75854</v>
       </c>
       <c r="N26">
-        <v>7.771801600000001</v>
+        <v>7.701460000000001</v>
       </c>
       <c r="O26">
-        <v>1.9429504</v>
+        <v>1.925365</v>
       </c>
       <c r="P26">
-        <v>5.828851200000001</v>
+        <v>5.776095000000001</v>
       </c>
       <c r="Q26">
-        <v>12.6188512</v>
+        <v>12.566095</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1855628647887632</v>
+        <v>0.1870497037758777</v>
       </c>
       <c r="T26">
-        <v>0.854772282706793</v>
+        <v>0.8638656048632481</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.603606779866633</v>
+        <v>5.379462508671967</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1506560278319083</v>
+        <v>0.1503302784243565</v>
       </c>
       <c r="C27">
-        <v>106.4153047073625</v>
+        <v>105.4939379822509</v>
       </c>
       <c r="D27">
-        <v>112.5153047073625</v>
+        <v>112.8659379822509</v>
       </c>
       <c r="E27">
-        <v>19.8</v>
+        <v>21.072</v>
       </c>
       <c r="F27">
-        <v>31.8</v>
+        <v>33.072</v>
       </c>
       <c r="G27">
         <v>25.7</v>
@@ -3501,28 +3501,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M27">
-        <v>1.75854</v>
+        <v>1.8288816</v>
       </c>
       <c r="N27">
-        <v>7.701460000000001</v>
+        <v>7.631118400000001</v>
       </c>
       <c r="O27">
-        <v>1.925365</v>
+        <v>1.9077796</v>
       </c>
       <c r="P27">
-        <v>5.776095000000001</v>
+        <v>5.723338800000001</v>
       </c>
       <c r="Q27">
-        <v>12.566095</v>
+        <v>12.5133388</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1870497037758777</v>
+        <v>0.1885767276004818</v>
       </c>
       <c r="T27">
-        <v>0.8638656048632481</v>
+        <v>0.8732046924833914</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.379462508671967</v>
+        <v>5.172560104492276</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1503302784243565</v>
+        <v>0.1500045290168047</v>
       </c>
       <c r="C28">
-        <v>105.4939379822509</v>
+        <v>104.5747634570877</v>
       </c>
       <c r="D28">
-        <v>112.8659379822509</v>
+        <v>113.2187634570877</v>
       </c>
       <c r="E28">
-        <v>21.072</v>
+        <v>22.344</v>
       </c>
       <c r="F28">
-        <v>33.072</v>
+        <v>34.344</v>
       </c>
       <c r="G28">
         <v>25.7</v>
@@ -3583,28 +3583,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M28">
-        <v>1.8288816</v>
+        <v>1.8992232</v>
       </c>
       <c r="N28">
-        <v>7.631118400000001</v>
+        <v>7.560776800000001</v>
       </c>
       <c r="O28">
-        <v>1.9077796</v>
+        <v>1.8901942</v>
       </c>
       <c r="P28">
-        <v>5.723338800000001</v>
+        <v>5.670582600000001</v>
       </c>
       <c r="Q28">
-        <v>12.5133388</v>
+        <v>12.4605826</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1885767276004818</v>
+        <v>0.1901455876942531</v>
       </c>
       <c r="T28">
-        <v>0.8732046924833914</v>
+        <v>0.8827996455177852</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.172560104492276</v>
+        <v>4.980983804325895</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1500045290168047</v>
+        <v>0.149678779609253</v>
       </c>
       <c r="C29">
-        <v>104.5747634570877</v>
+        <v>103.6578017551753</v>
       </c>
       <c r="D29">
-        <v>113.2187634570877</v>
+        <v>113.5738017551753</v>
       </c>
       <c r="E29">
-        <v>22.344</v>
+        <v>23.61600000000001</v>
       </c>
       <c r="F29">
-        <v>34.344</v>
+        <v>35.61600000000001</v>
       </c>
       <c r="G29">
         <v>25.7</v>
@@ -3665,28 +3665,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M29">
-        <v>1.8992232</v>
+        <v>1.9695648</v>
       </c>
       <c r="N29">
-        <v>7.560776800000001</v>
+        <v>7.4904352</v>
       </c>
       <c r="O29">
-        <v>1.8901942</v>
+        <v>1.8726088</v>
       </c>
       <c r="P29">
-        <v>5.670582600000001</v>
+        <v>5.6178264</v>
       </c>
       <c r="Q29">
-        <v>12.4605826</v>
+        <v>12.4078264</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1901455876942531</v>
+        <v>0.1917580272350736</v>
       </c>
       <c r="T29">
-        <v>0.8827996455177852</v>
+        <v>0.8926611250253564</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.980983804325895</v>
+        <v>4.803091525599969</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.149678779609253</v>
+        <v>0.1493530302017012</v>
       </c>
       <c r="C30">
-        <v>103.6578017551753</v>
+        <v>102.7430737593174</v>
       </c>
       <c r="D30">
-        <v>113.5738017551753</v>
+        <v>113.9310737593174</v>
       </c>
       <c r="E30">
-        <v>23.61600000000001</v>
+        <v>24.88800000000001</v>
       </c>
       <c r="F30">
-        <v>35.61600000000001</v>
+        <v>36.88800000000001</v>
       </c>
       <c r="G30">
         <v>25.7</v>
@@ -3747,28 +3747,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M30">
-        <v>1.9695648</v>
+        <v>2.0399064</v>
       </c>
       <c r="N30">
-        <v>7.4904352</v>
+        <v>7.4200936</v>
       </c>
       <c r="O30">
-        <v>1.8726088</v>
+        <v>1.8550234</v>
       </c>
       <c r="P30">
-        <v>5.6178264</v>
+        <v>5.5650702</v>
       </c>
       <c r="Q30">
-        <v>12.4078264</v>
+        <v>12.3550702</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1917580272350736</v>
+        <v>0.1934158876080299</v>
       </c>
       <c r="T30">
-        <v>0.8926611250253564</v>
+        <v>0.9028003926880706</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.803091525599969</v>
+        <v>4.637467679889625</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1493530302017012</v>
+        <v>0.1495897807941494</v>
       </c>
       <c r="C31">
-        <v>102.7430737593174</v>
+        <v>101.211190281345</v>
       </c>
       <c r="D31">
-        <v>113.9310737593174</v>
+        <v>113.6711902813449</v>
       </c>
       <c r="E31">
-        <v>24.888</v>
+        <v>26.16</v>
       </c>
       <c r="F31">
-        <v>36.888</v>
+        <v>38.16</v>
       </c>
       <c r="G31">
         <v>25.7</v>
@@ -3829,45 +3829,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M31">
-        <v>2.0399064</v>
+        <v>2.205648</v>
       </c>
       <c r="N31">
-        <v>7.420093600000001</v>
+        <v>7.254352000000001</v>
       </c>
       <c r="O31">
-        <v>1.8550234</v>
+        <v>1.813588</v>
       </c>
       <c r="P31">
-        <v>5.565070200000001</v>
+        <v>5.440764000000001</v>
       </c>
       <c r="Q31">
-        <v>12.3550702</v>
+        <v>12.230764</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1934158876080299</v>
+        <v>0.1951211154202135</v>
       </c>
       <c r="T31">
-        <v>0.9028003926880706</v>
+        <v>0.9132293537125766</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.637467679889626</v>
+        <v>4.288988995524218</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1495897807941494</v>
+        <v>0.1492827813865977</v>
       </c>
       <c r="C32">
-        <v>101.211190281345</v>
+        <v>100.2764153501388</v>
       </c>
       <c r="D32">
-        <v>113.6711902813449</v>
+        <v>114.0084153501388</v>
       </c>
       <c r="E32">
-        <v>26.16</v>
+        <v>27.432</v>
       </c>
       <c r="F32">
-        <v>38.16</v>
+        <v>39.432</v>
       </c>
       <c r="G32">
         <v>25.7</v>
@@ -3911,28 +3911,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M32">
-        <v>2.205648</v>
+        <v>2.2791696</v>
       </c>
       <c r="N32">
-        <v>7.254352000000001</v>
+        <v>7.180830400000001</v>
       </c>
       <c r="O32">
-        <v>1.813588</v>
+        <v>1.7952076</v>
       </c>
       <c r="P32">
-        <v>5.440764000000001</v>
+        <v>5.3856228</v>
       </c>
       <c r="Q32">
-        <v>12.230764</v>
+        <v>12.1756228</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1951211154202135</v>
+        <v>0.1968757701255039</v>
       </c>
       <c r="T32">
-        <v>0.9132293537125766</v>
+        <v>0.9239606034624306</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.288988995524218</v>
+        <v>4.15063451179763</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1492827813865977</v>
+        <v>0.148975781979046</v>
       </c>
       <c r="C33">
-        <v>100.2764153501388</v>
+        <v>99.34364724445592</v>
       </c>
       <c r="D33">
-        <v>114.0084153501388</v>
+        <v>114.3476472444559</v>
       </c>
       <c r="E33">
-        <v>27.432</v>
+        <v>28.704</v>
       </c>
       <c r="F33">
-        <v>39.432</v>
+        <v>40.704</v>
       </c>
       <c r="G33">
         <v>25.7</v>
@@ -3993,28 +3993,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M33">
-        <v>2.2791696</v>
+        <v>2.3526912</v>
       </c>
       <c r="N33">
-        <v>7.180830400000001</v>
+        <v>7.1073088</v>
       </c>
       <c r="O33">
-        <v>1.7952076</v>
+        <v>1.7768272</v>
       </c>
       <c r="P33">
-        <v>5.3856228</v>
+        <v>5.330481600000001</v>
       </c>
       <c r="Q33">
-        <v>12.1756228</v>
+        <v>12.1204816</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1968757701255039</v>
+        <v>0.1986820323221264</v>
       </c>
       <c r="T33">
-        <v>0.9239606034624306</v>
+        <v>0.9350074782049275</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.15063451179763</v>
+        <v>4.020927183303954</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.148975781979046</v>
+        <v>0.1495350325714942</v>
       </c>
       <c r="C34">
-        <v>99.34364724445592</v>
+        <v>97.45518250847147</v>
       </c>
       <c r="D34">
-        <v>114.3476472444559</v>
+        <v>113.7311825084715</v>
       </c>
       <c r="E34">
-        <v>28.704</v>
+        <v>29.97600000000001</v>
       </c>
       <c r="F34">
-        <v>40.704</v>
+        <v>41.97600000000001</v>
       </c>
       <c r="G34">
         <v>25.7</v>
@@ -4075,45 +4075,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M34">
-        <v>2.3526912</v>
+        <v>2.573128800000001</v>
       </c>
       <c r="N34">
-        <v>7.1073088</v>
+        <v>6.8868712</v>
       </c>
       <c r="O34">
-        <v>1.7768272</v>
+        <v>1.7217178</v>
       </c>
       <c r="P34">
-        <v>5.330481600000001</v>
+        <v>5.165153399999999</v>
       </c>
       <c r="Q34">
-        <v>12.1204816</v>
+        <v>11.9551534</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1986820323221264</v>
+        <v>0.200542212793275</v>
       </c>
       <c r="T34">
-        <v>0.9350074782049275</v>
+        <v>0.9463841104024242</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.020927183303954</v>
+        <v>3.67645801484947</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1495350325714942</v>
+        <v>0.1492542831639425</v>
       </c>
       <c r="C35">
-        <v>97.45518250847147</v>
+        <v>96.4918208860514</v>
       </c>
       <c r="D35">
-        <v>113.7311825084715</v>
+        <v>114.0398208860514</v>
       </c>
       <c r="E35">
-        <v>29.97600000000001</v>
+        <v>31.248</v>
       </c>
       <c r="F35">
-        <v>41.97600000000001</v>
+        <v>43.248</v>
       </c>
       <c r="G35">
         <v>25.7</v>
@@ -4157,28 +4157,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M35">
-        <v>2.573128800000001</v>
+        <v>2.6511024</v>
       </c>
       <c r="N35">
-        <v>6.8868712</v>
+        <v>6.808897600000001</v>
       </c>
       <c r="O35">
-        <v>1.7217178</v>
+        <v>1.7022244</v>
       </c>
       <c r="P35">
-        <v>5.165153399999999</v>
+        <v>5.1066732</v>
       </c>
       <c r="Q35">
-        <v>11.9551534</v>
+        <v>11.8966732</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.200542212793275</v>
+        <v>0.2024587623696098</v>
       </c>
       <c r="T35">
-        <v>0.9463841104024242</v>
+        <v>0.958105489030148</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.67645801484947</v>
+        <v>3.568326896765663</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1492542831639425</v>
+        <v>0.1497085337563907</v>
       </c>
       <c r="C36">
-        <v>96.4918208860514</v>
+        <v>94.72127996426696</v>
       </c>
       <c r="D36">
-        <v>114.0398208860514</v>
+        <v>113.541279964267</v>
       </c>
       <c r="E36">
-        <v>31.248</v>
+        <v>32.52</v>
       </c>
       <c r="F36">
-        <v>43.248</v>
+        <v>44.52</v>
       </c>
       <c r="G36">
         <v>25.7</v>
@@ -4239,45 +4239,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M36">
-        <v>2.6511024</v>
+        <v>2.853732</v>
       </c>
       <c r="N36">
-        <v>6.808897600000001</v>
+        <v>6.606268</v>
       </c>
       <c r="O36">
-        <v>1.7022244</v>
+        <v>1.651567</v>
       </c>
       <c r="P36">
-        <v>5.1066732</v>
+        <v>4.954701</v>
       </c>
       <c r="Q36">
-        <v>11.8966732</v>
+        <v>11.744701</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2024587623696098</v>
+        <v>0.2044342827021396</v>
       </c>
       <c r="T36">
-        <v>0.958105489030148</v>
+        <v>0.9701875254618019</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.568326896765663</v>
+        <v>3.314957396139511</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1497085337563907</v>
+        <v>0.1494487843488389</v>
       </c>
       <c r="C37">
-        <v>94.72127996426696</v>
+        <v>93.73382049591598</v>
       </c>
       <c r="D37">
-        <v>113.541279964267</v>
+        <v>113.825820495916</v>
       </c>
       <c r="E37">
-        <v>32.52</v>
+        <v>33.79200000000001</v>
       </c>
       <c r="F37">
-        <v>44.52</v>
+        <v>45.79200000000001</v>
       </c>
       <c r="G37">
         <v>25.7</v>
@@ -4321,28 +4321,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M37">
-        <v>2.853732</v>
+        <v>2.935267200000001</v>
       </c>
       <c r="N37">
-        <v>6.606268</v>
+        <v>6.524732800000001</v>
       </c>
       <c r="O37">
-        <v>1.651567</v>
+        <v>1.6311832</v>
       </c>
       <c r="P37">
-        <v>4.954701</v>
+        <v>4.8935496</v>
       </c>
       <c r="Q37">
-        <v>11.744701</v>
+        <v>11.6835496</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2044342827021396</v>
+        <v>0.2064715380450609</v>
       </c>
       <c r="T37">
-        <v>0.9701875254618019</v>
+        <v>0.9826471255319448</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.314957396139511</v>
+        <v>3.222875246246747</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.149448784348839</v>
+        <v>0.1491890349412872</v>
       </c>
       <c r="C38">
-        <v>93.73382049591592</v>
+        <v>92.747790758185</v>
       </c>
       <c r="D38">
-        <v>113.8258204959159</v>
+        <v>114.111790758185</v>
       </c>
       <c r="E38">
-        <v>33.792</v>
+        <v>35.064</v>
       </c>
       <c r="F38">
-        <v>45.792</v>
+        <v>47.064</v>
       </c>
       <c r="G38">
         <v>25.7</v>
@@ -4403,28 +4403,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M38">
-        <v>2.9352672</v>
+        <v>3.0168024</v>
       </c>
       <c r="N38">
-        <v>6.524732800000001</v>
+        <v>6.443197600000001</v>
       </c>
       <c r="O38">
-        <v>1.6311832</v>
+        <v>1.6107994</v>
       </c>
       <c r="P38">
-        <v>4.8935496</v>
+        <v>4.832398200000001</v>
       </c>
       <c r="Q38">
-        <v>11.6835496</v>
+        <v>11.6223982</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2064715380450609</v>
+        <v>0.2085734681607733</v>
       </c>
       <c r="T38">
-        <v>0.9826471255319448</v>
+        <v>0.9955022684614574</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.222875246246747</v>
+        <v>3.1357705098617</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1491890349412872</v>
+        <v>0.1489292855337354</v>
       </c>
       <c r="C39">
-        <v>92.747790758185</v>
+        <v>91.76320155416509</v>
       </c>
       <c r="D39">
-        <v>114.111790758185</v>
+        <v>114.3992015541651</v>
       </c>
       <c r="E39">
-        <v>35.064</v>
+        <v>36.336</v>
       </c>
       <c r="F39">
-        <v>47.064</v>
+        <v>48.336</v>
       </c>
       <c r="G39">
         <v>25.7</v>
@@ -4485,28 +4485,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M39">
-        <v>3.0168024</v>
+        <v>3.0983376</v>
       </c>
       <c r="N39">
-        <v>6.443197600000001</v>
+        <v>6.3616624</v>
       </c>
       <c r="O39">
-        <v>1.6107994</v>
+        <v>1.5904156</v>
       </c>
       <c r="P39">
-        <v>4.832398200000001</v>
+        <v>4.7712468</v>
       </c>
       <c r="Q39">
-        <v>11.6223982</v>
+        <v>11.5612468</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2085734681607733</v>
+        <v>0.2107432024737668</v>
       </c>
       <c r="T39">
-        <v>0.9955022684614574</v>
+        <v>1.008772093420954</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.1357705098617</v>
+        <v>3.053250233286392</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1489292855337354</v>
+        <v>0.1509510361261837</v>
       </c>
       <c r="C40">
-        <v>91.76320155416509</v>
+        <v>88.29163546296473</v>
       </c>
       <c r="D40">
-        <v>114.3992015541651</v>
+        <v>112.1996354629647</v>
       </c>
       <c r="E40">
-        <v>36.336</v>
+        <v>37.608</v>
       </c>
       <c r="F40">
-        <v>48.336</v>
+        <v>49.608</v>
       </c>
       <c r="G40">
         <v>25.7</v>
@@ -4567,45 +4567,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M40">
-        <v>3.0983376</v>
+        <v>3.566815200000001</v>
       </c>
       <c r="N40">
-        <v>6.3616624</v>
+        <v>5.8931848</v>
       </c>
       <c r="O40">
-        <v>1.5904156</v>
+        <v>1.4732962</v>
       </c>
       <c r="P40">
-        <v>4.7712468</v>
+        <v>4.4198886</v>
       </c>
       <c r="Q40">
-        <v>11.5612468</v>
+        <v>11.2098886</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2107432024737668</v>
+        <v>0.2129840756166946</v>
       </c>
       <c r="T40">
-        <v>1.008772093420954</v>
+        <v>1.022476994608631</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.053250233286392</v>
+        <v>2.652225997018292</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1509510361261837</v>
+        <v>0.1507497867186319</v>
       </c>
       <c r="C41">
-        <v>88.29163546296473</v>
+        <v>87.23478702134742</v>
       </c>
       <c r="D41">
-        <v>112.1996354629647</v>
+        <v>112.4147870213474</v>
       </c>
       <c r="E41">
-        <v>37.608</v>
+        <v>38.88</v>
       </c>
       <c r="F41">
-        <v>49.608</v>
+        <v>50.88</v>
       </c>
       <c r="G41">
         <v>25.7</v>
@@ -4649,28 +4649,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M41">
-        <v>3.566815200000001</v>
+        <v>3.658272000000001</v>
       </c>
       <c r="N41">
-        <v>5.8931848</v>
+        <v>5.801728000000001</v>
       </c>
       <c r="O41">
-        <v>1.4732962</v>
+        <v>1.450432</v>
       </c>
       <c r="P41">
-        <v>4.4198886</v>
+        <v>4.351296</v>
       </c>
       <c r="Q41">
-        <v>11.2098886</v>
+        <v>11.141296</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2129840756166946</v>
+        <v>0.2152996445310532</v>
       </c>
       <c r="T41">
-        <v>1.022476994608631</v>
+        <v>1.036638725835898</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.652225997018292</v>
+        <v>2.585920347092835</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1507497867186319</v>
+        <v>0.1505485373110802</v>
       </c>
       <c r="C42">
-        <v>87.23478702134742</v>
+        <v>86.17876530485236</v>
       </c>
       <c r="D42">
-        <v>112.4147870213474</v>
+        <v>112.6307653048524</v>
       </c>
       <c r="E42">
-        <v>38.88</v>
+        <v>40.15200000000001</v>
       </c>
       <c r="F42">
-        <v>50.88</v>
+        <v>52.15200000000001</v>
       </c>
       <c r="G42">
         <v>25.7</v>
@@ -4731,28 +4731,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M42">
-        <v>3.658272000000001</v>
+        <v>3.749728800000001</v>
       </c>
       <c r="N42">
-        <v>5.801728000000001</v>
+        <v>5.710271199999999</v>
       </c>
       <c r="O42">
-        <v>1.450432</v>
+        <v>1.4275678</v>
       </c>
       <c r="P42">
-        <v>4.351296</v>
+        <v>4.282703399999999</v>
       </c>
       <c r="Q42">
-        <v>11.141296</v>
+        <v>11.0727034</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2152996445310532</v>
+        <v>0.2176937073069156</v>
       </c>
       <c r="T42">
-        <v>1.036638725835898</v>
+        <v>1.051280515748834</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.585920347092835</v>
+        <v>2.52284911911496</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1505485373110802</v>
+        <v>0.1515757879035284</v>
       </c>
       <c r="C43">
-        <v>86.17876530485236</v>
+        <v>83.81294201428202</v>
       </c>
       <c r="D43">
-        <v>112.6307653048524</v>
+        <v>111.536942014282</v>
       </c>
       <c r="E43">
-        <v>40.15200000000001</v>
+        <v>41.42400000000001</v>
       </c>
       <c r="F43">
-        <v>52.15200000000001</v>
+        <v>53.42400000000001</v>
       </c>
       <c r="G43">
         <v>25.7</v>
@@ -4813,45 +4813,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M43">
-        <v>3.749728800000001</v>
+        <v>4.049539200000001</v>
       </c>
       <c r="N43">
-        <v>5.710271199999999</v>
+        <v>5.4104608</v>
       </c>
       <c r="O43">
-        <v>1.4275678</v>
+        <v>1.3526152</v>
       </c>
       <c r="P43">
-        <v>4.282703399999999</v>
+        <v>4.0578456</v>
       </c>
       <c r="Q43">
-        <v>11.0727034</v>
+        <v>10.8478456</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2176937073069156</v>
+        <v>0.2201703239716007</v>
       </c>
       <c r="T43">
-        <v>1.051280515748834</v>
+        <v>1.066427194969113</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.52284911911496</v>
+        <v>2.336068261791366</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1515757879035285</v>
+        <v>0.1514037884959767</v>
       </c>
       <c r="C44">
-        <v>83.81294201428196</v>
+        <v>82.72260489039488</v>
       </c>
       <c r="D44">
-        <v>111.536942014282</v>
+        <v>111.7186048903949</v>
       </c>
       <c r="E44">
-        <v>41.424</v>
+        <v>42.696</v>
       </c>
       <c r="F44">
-        <v>53.424</v>
+        <v>54.696</v>
       </c>
       <c r="G44">
         <v>25.7</v>
@@ -4895,28 +4895,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M44">
-        <v>4.0495392</v>
+        <v>4.1459568</v>
       </c>
       <c r="N44">
-        <v>5.410460800000001</v>
+        <v>5.3140432</v>
       </c>
       <c r="O44">
-        <v>1.3526152</v>
+        <v>1.3285108</v>
       </c>
       <c r="P44">
-        <v>4.0578456</v>
+        <v>3.9855324</v>
       </c>
       <c r="Q44">
-        <v>10.8478456</v>
+        <v>10.7755324</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2201703239716007</v>
+        <v>0.2227338394666257</v>
       </c>
       <c r="T44">
-        <v>1.066427194969113</v>
+        <v>1.082105336618174</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.336068261791366</v>
+        <v>2.281741092912497</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1514037884959767</v>
+        <v>0.1512317890884249</v>
       </c>
       <c r="C45">
-        <v>82.72260489039488</v>
+        <v>81.63286048920232</v>
       </c>
       <c r="D45">
-        <v>111.7186048903949</v>
+        <v>111.9008604892023</v>
       </c>
       <c r="E45">
-        <v>42.696</v>
+        <v>43.968</v>
       </c>
       <c r="F45">
-        <v>54.696</v>
+        <v>55.968</v>
       </c>
       <c r="G45">
         <v>25.7</v>
@@ -4977,28 +4977,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M45">
-        <v>4.1459568</v>
+        <v>4.242374400000001</v>
       </c>
       <c r="N45">
-        <v>5.3140432</v>
+        <v>5.2176256</v>
       </c>
       <c r="O45">
-        <v>1.3285108</v>
+        <v>1.3044064</v>
       </c>
       <c r="P45">
-        <v>3.9855324</v>
+        <v>3.9132192</v>
       </c>
       <c r="Q45">
-        <v>10.7755324</v>
+        <v>10.7032192</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2227338394666257</v>
+        <v>0.225388909086473</v>
       </c>
       <c r="T45">
-        <v>1.082105336618174</v>
+        <v>1.098343411897558</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.281741092912497</v>
+        <v>2.229883340800849</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1512317890884249</v>
+        <v>0.1510597896808732</v>
       </c>
       <c r="C46">
-        <v>81.63286048920232</v>
+        <v>80.54371171631408</v>
       </c>
       <c r="D46">
-        <v>111.9008604892023</v>
+        <v>112.0837117163141</v>
       </c>
       <c r="E46">
-        <v>43.968</v>
+        <v>45.24</v>
       </c>
       <c r="F46">
-        <v>55.968</v>
+        <v>57.24</v>
       </c>
       <c r="G46">
         <v>25.7</v>
@@ -5059,28 +5059,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M46">
-        <v>4.242374400000001</v>
+        <v>4.338792000000001</v>
       </c>
       <c r="N46">
-        <v>5.2176256</v>
+        <v>5.121208</v>
       </c>
       <c r="O46">
-        <v>1.3044064</v>
+        <v>1.280302</v>
       </c>
       <c r="P46">
-        <v>3.9132192</v>
+        <v>3.840906</v>
       </c>
       <c r="Q46">
-        <v>10.7032192</v>
+        <v>10.630906</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.225388909086473</v>
+        <v>0.2281405266924967</v>
       </c>
       <c r="T46">
-        <v>1.098343411897558</v>
+        <v>1.115171962641648</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.229883340800849</v>
+        <v>2.180330377671942</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1510597896808732</v>
+        <v>0.1508877902733214</v>
       </c>
       <c r="C47">
-        <v>80.54371171631408</v>
+        <v>79.45516149636245</v>
       </c>
       <c r="D47">
-        <v>112.0837117163141</v>
+        <v>112.2671614963625</v>
       </c>
       <c r="E47">
-        <v>45.24</v>
+        <v>46.512</v>
       </c>
       <c r="F47">
-        <v>57.24</v>
+        <v>58.512</v>
       </c>
       <c r="G47">
         <v>25.7</v>
@@ -5141,28 +5141,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M47">
-        <v>4.338792000000001</v>
+        <v>4.4352096</v>
       </c>
       <c r="N47">
-        <v>5.121208</v>
+        <v>5.024790400000001</v>
       </c>
       <c r="O47">
-        <v>1.280302</v>
+        <v>1.2561976</v>
       </c>
       <c r="P47">
-        <v>3.840906</v>
+        <v>3.7685928</v>
       </c>
       <c r="Q47">
-        <v>10.630906</v>
+        <v>10.5585928</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2281405266924967</v>
+        <v>0.2309940560617063</v>
       </c>
       <c r="T47">
-        <v>1.115171962641648</v>
+        <v>1.132623793042925</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.180330377671942</v>
+        <v>2.132931891200813</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1508877902733214</v>
+        <v>0.1507157908657696</v>
       </c>
       <c r="C48">
-        <v>79.45516149636245</v>
+        <v>78.36721277315833</v>
       </c>
       <c r="D48">
-        <v>112.2671614963625</v>
+        <v>112.4512127731583</v>
       </c>
       <c r="E48">
-        <v>46.512</v>
+        <v>47.78400000000001</v>
       </c>
       <c r="F48">
-        <v>58.512</v>
+        <v>59.78400000000001</v>
       </c>
       <c r="G48">
         <v>25.7</v>
@@ -5223,28 +5223,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M48">
-        <v>4.4352096</v>
+        <v>4.531627200000001</v>
       </c>
       <c r="N48">
-        <v>5.024790400000001</v>
+        <v>4.9283728</v>
       </c>
       <c r="O48">
-        <v>1.2561976</v>
+        <v>1.2320932</v>
       </c>
       <c r="P48">
-        <v>3.7685928</v>
+        <v>3.6962796</v>
       </c>
       <c r="Q48">
-        <v>10.5585928</v>
+        <v>10.4862796</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2309940560617063</v>
+        <v>0.233955265784471</v>
       </c>
       <c r="T48">
-        <v>1.132623793042925</v>
+        <v>1.150734183081987</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.132931891200813</v>
+        <v>2.087550361600795</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1507157908657696</v>
+        <v>0.1505437914582179</v>
       </c>
       <c r="C49">
-        <v>78.36721277315833</v>
+        <v>77.27986850984865</v>
       </c>
       <c r="D49">
-        <v>112.4512127731583</v>
+        <v>112.6358685098487</v>
       </c>
       <c r="E49">
-        <v>47.78400000000001</v>
+        <v>49.056</v>
       </c>
       <c r="F49">
-        <v>59.78400000000001</v>
+        <v>61.056</v>
       </c>
       <c r="G49">
         <v>25.7</v>
@@ -5305,28 +5305,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M49">
-        <v>4.531627200000001</v>
+        <v>4.628044800000001</v>
       </c>
       <c r="N49">
-        <v>4.9283728</v>
+        <v>4.8319552</v>
       </c>
       <c r="O49">
-        <v>1.2320932</v>
+        <v>1.2079888</v>
       </c>
       <c r="P49">
-        <v>3.6962796</v>
+        <v>3.6239664</v>
       </c>
       <c r="Q49">
-        <v>10.4862796</v>
+        <v>10.4139664</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.233955265784471</v>
+        <v>0.2370303681888805</v>
       </c>
       <c r="T49">
-        <v>1.150734183081987</v>
+        <v>1.16954112658409</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.087550361600795</v>
+        <v>2.044059729067445</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1505437914582179</v>
+        <v>0.1503717920506661</v>
       </c>
       <c r="C50">
-        <v>77.27986850984867</v>
+        <v>76.19313168907567</v>
       </c>
       <c r="D50">
-        <v>112.6358685098487</v>
+        <v>112.8211316890757</v>
       </c>
       <c r="E50">
-        <v>49.056</v>
+        <v>50.328</v>
       </c>
       <c r="F50">
-        <v>61.056</v>
+        <v>62.328</v>
       </c>
       <c r="G50">
         <v>25.7</v>
@@ -5387,28 +5387,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M50">
-        <v>4.628044800000001</v>
+        <v>4.7244624</v>
       </c>
       <c r="N50">
-        <v>4.8319552</v>
+        <v>4.735537600000001</v>
       </c>
       <c r="O50">
-        <v>1.2079888</v>
+        <v>1.1838844</v>
       </c>
       <c r="P50">
-        <v>3.6239664</v>
+        <v>3.551653200000001</v>
       </c>
       <c r="Q50">
-        <v>10.4139664</v>
+        <v>10.3416532</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2370303681888805</v>
+        <v>0.2402260628444434</v>
       </c>
       <c r="T50">
-        <v>1.16954112658409</v>
+        <v>1.189085597282353</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.044059729067445</v>
+        <v>2.0023442243926</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1503717920506661</v>
+        <v>0.1555247926431144</v>
       </c>
       <c r="C51">
-        <v>76.19313168907567</v>
+        <v>69.62271786271816</v>
       </c>
       <c r="D51">
-        <v>112.8211316890757</v>
+        <v>107.5227178627182</v>
       </c>
       <c r="E51">
-        <v>50.328</v>
+        <v>51.6</v>
       </c>
       <c r="F51">
-        <v>62.328</v>
+        <v>63.6</v>
       </c>
       <c r="G51">
         <v>25.7</v>
@@ -5469,45 +5469,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M51">
-        <v>4.7244624</v>
+        <v>5.724</v>
       </c>
       <c r="N51">
-        <v>4.735537600000001</v>
+        <v>3.736000000000001</v>
       </c>
       <c r="O51">
-        <v>1.1838844</v>
+        <v>0.9340000000000002</v>
       </c>
       <c r="P51">
-        <v>3.551653200000001</v>
+        <v>2.802</v>
       </c>
       <c r="Q51">
-        <v>10.3416532</v>
+        <v>9.592000000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2402260628444434</v>
+        <v>0.2435495852862288</v>
       </c>
       <c r="T51">
-        <v>1.189085597282353</v>
+        <v>1.209411846808548</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.0023442243926</v>
+        <v>1.652690426275332</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1555247926431144</v>
+        <v>0.1554592932355626</v>
       </c>
       <c r="C52">
-        <v>69.62271786271816</v>
+        <v>68.41494109552012</v>
       </c>
       <c r="D52">
-        <v>107.5227178627182</v>
+        <v>107.5869410955201</v>
       </c>
       <c r="E52">
-        <v>51.6</v>
+        <v>52.872</v>
       </c>
       <c r="F52">
-        <v>63.6</v>
+        <v>64.872</v>
       </c>
       <c r="G52">
         <v>25.7</v>
@@ -5551,28 +5551,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M52">
-        <v>5.724</v>
+        <v>5.83848</v>
       </c>
       <c r="N52">
-        <v>3.736000000000001</v>
+        <v>3.621520000000001</v>
       </c>
       <c r="O52">
-        <v>0.9340000000000002</v>
+        <v>0.9053800000000003</v>
       </c>
       <c r="P52">
-        <v>2.802</v>
+        <v>2.716140000000001</v>
       </c>
       <c r="Q52">
-        <v>9.592000000000001</v>
+        <v>9.506140000000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2435495852862288</v>
+        <v>0.2470087617052298</v>
       </c>
       <c r="T52">
-        <v>1.209411846808548</v>
+        <v>1.230567739172545</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.652690426275332</v>
+        <v>1.620284731642482</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1554592932355626</v>
+        <v>0.1553937938280108</v>
       </c>
       <c r="C53">
-        <v>68.41494109552012</v>
+        <v>67.20724109514532</v>
       </c>
       <c r="D53">
-        <v>107.5869410955201</v>
+        <v>107.6512410951453</v>
       </c>
       <c r="E53">
-        <v>52.872</v>
+        <v>54.14400000000001</v>
       </c>
       <c r="F53">
-        <v>64.872</v>
+        <v>66.14400000000001</v>
       </c>
       <c r="G53">
         <v>25.7</v>
@@ -5633,28 +5633,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M53">
-        <v>5.83848</v>
+        <v>5.95296</v>
       </c>
       <c r="N53">
-        <v>3.621520000000001</v>
+        <v>3.507040000000001</v>
       </c>
       <c r="O53">
-        <v>0.9053800000000003</v>
+        <v>0.8767600000000002</v>
       </c>
       <c r="P53">
-        <v>2.716140000000001</v>
+        <v>2.630280000000001</v>
       </c>
       <c r="Q53">
-        <v>9.506140000000002</v>
+        <v>9.420280000000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2470087617052298</v>
+        <v>0.2506120704750226</v>
       </c>
       <c r="T53">
-        <v>1.230567739172545</v>
+        <v>1.25260512705171</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.620284731642482</v>
+        <v>1.589125409880127</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1553937938280108</v>
+        <v>0.1553282944204591</v>
       </c>
       <c r="C54">
-        <v>67.20724109514532</v>
+        <v>65.9996179993165</v>
       </c>
       <c r="D54">
-        <v>107.6512410951453</v>
+        <v>107.7156179993165</v>
       </c>
       <c r="E54">
-        <v>54.14400000000001</v>
+        <v>55.41600000000001</v>
       </c>
       <c r="F54">
-        <v>66.14400000000001</v>
+        <v>67.41600000000001</v>
       </c>
       <c r="G54">
         <v>25.7</v>
@@ -5715,28 +5715,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M54">
-        <v>5.95296</v>
+        <v>6.06744</v>
       </c>
       <c r="N54">
-        <v>3.507040000000001</v>
+        <v>3.39256</v>
       </c>
       <c r="O54">
-        <v>0.8767600000000002</v>
+        <v>0.8481400000000001</v>
       </c>
       <c r="P54">
-        <v>2.630280000000001</v>
+        <v>2.544420000000001</v>
       </c>
       <c r="Q54">
-        <v>9.420280000000002</v>
+        <v>9.334420000000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2506120704750226</v>
+        <v>0.2543687115328918</v>
       </c>
       <c r="T54">
-        <v>1.25260512705171</v>
+        <v>1.275580276117222</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.589125409880127</v>
+        <v>1.559141911580502</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1553282944204591</v>
+        <v>0.1552627950129074</v>
       </c>
       <c r="C55">
-        <v>65.9996179993165</v>
+        <v>64.79207194608621</v>
       </c>
       <c r="D55">
-        <v>107.7156179993165</v>
+        <v>107.7800719460862</v>
       </c>
       <c r="E55">
-        <v>55.41600000000001</v>
+        <v>56.688</v>
       </c>
       <c r="F55">
-        <v>67.41600000000001</v>
+        <v>68.688</v>
       </c>
       <c r="G55">
         <v>25.7</v>
@@ -5797,28 +5797,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M55">
-        <v>6.06744</v>
+        <v>6.18192</v>
       </c>
       <c r="N55">
-        <v>3.39256</v>
+        <v>3.278080000000001</v>
       </c>
       <c r="O55">
-        <v>0.8481400000000001</v>
+        <v>0.8195200000000002</v>
       </c>
       <c r="P55">
-        <v>2.544420000000001</v>
+        <v>2.458560000000001</v>
       </c>
       <c r="Q55">
-        <v>9.334420000000001</v>
+        <v>9.248560000000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2543687115328918</v>
+        <v>0.2582886848106682</v>
       </c>
       <c r="T55">
-        <v>1.275580276117222</v>
+        <v>1.299554344707321</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.559141911580502</v>
+        <v>1.5302689132179</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1552627950129074</v>
+        <v>0.1551972956053556</v>
       </c>
       <c r="C56">
-        <v>64.79207194608621</v>
+        <v>63.58460307383748</v>
       </c>
       <c r="D56">
-        <v>107.7800719460862</v>
+        <v>107.8446030738375</v>
       </c>
       <c r="E56">
-        <v>56.688</v>
+        <v>57.96000000000001</v>
       </c>
       <c r="F56">
-        <v>68.688</v>
+        <v>69.96000000000001</v>
       </c>
       <c r="G56">
         <v>25.7</v>
@@ -5879,28 +5879,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M56">
-        <v>6.18192</v>
+        <v>6.2964</v>
       </c>
       <c r="N56">
-        <v>3.278080000000001</v>
+        <v>3.163600000000001</v>
       </c>
       <c r="O56">
-        <v>0.8195200000000002</v>
+        <v>0.7909000000000002</v>
       </c>
       <c r="P56">
-        <v>2.458560000000001</v>
+        <v>2.3727</v>
       </c>
       <c r="Q56">
-        <v>9.248560000000001</v>
+        <v>9.162700000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2582886848106682</v>
+        <v>0.2623828791230124</v>
       </c>
       <c r="T56">
-        <v>1.299554344707321</v>
+        <v>1.324593927456981</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.5302689132179</v>
+        <v>1.502445842068484</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1551972956053556</v>
+        <v>0.1824551544560203</v>
       </c>
       <c r="C57">
-        <v>63.58460307383748</v>
+        <v>40.80142788184222</v>
       </c>
       <c r="D57">
-        <v>107.8446030738375</v>
+        <v>86.33342788184223</v>
       </c>
       <c r="E57">
-        <v>57.96000000000001</v>
+        <v>59.23200000000001</v>
       </c>
       <c r="F57">
-        <v>69.96000000000001</v>
+        <v>71.23200000000001</v>
       </c>
       <c r="G57">
         <v>25.7</v>
@@ -5961,45 +5961,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M57">
-        <v>6.2964</v>
+        <v>10.4568576</v>
       </c>
       <c r="N57">
-        <v>3.163600000000001</v>
+        <v>-0.996857600000002</v>
       </c>
       <c r="O57">
-        <v>0.7909000000000002</v>
+        <v>-0.2492144000000005</v>
       </c>
       <c r="P57">
-        <v>2.3727</v>
+        <v>-0.7476432000000015</v>
       </c>
       <c r="Q57">
-        <v>9.162700000000001</v>
+        <v>6.042356799999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2623828791230124</v>
+        <v>0.2700907312536769</v>
       </c>
       <c r="T57">
-        <v>1.324593927456981</v>
+        <v>1.371734191578299</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.25</v>
+        <v>0.2261673717350803</v>
       </c>
       <c r="W57">
-        <v>0.0675</v>
+        <v>0.1135986298292902</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.502445842068484</v>
+        <v>0.9046694869403211</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1824551544560203</v>
+        <v>0.1834651544560204</v>
       </c>
       <c r="C58">
-        <v>40.80142788184222</v>
+        <v>38.89603040006685</v>
       </c>
       <c r="D58">
-        <v>86.33342788184223</v>
+        <v>85.70003040006685</v>
       </c>
       <c r="E58">
-        <v>59.23200000000001</v>
+        <v>60.504</v>
       </c>
       <c r="F58">
-        <v>71.23200000000001</v>
+        <v>72.504</v>
       </c>
       <c r="G58">
         <v>25.7</v>
@@ -6043,37 +6043,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M58">
-        <v>10.4568576</v>
+        <v>10.6435872</v>
       </c>
       <c r="N58">
-        <v>-0.996857600000002</v>
+        <v>-1.183587200000002</v>
       </c>
       <c r="O58">
-        <v>-0.2492144000000005</v>
+        <v>-0.2958968000000004</v>
       </c>
       <c r="P58">
-        <v>-0.7476432000000015</v>
+        <v>-0.8876904000000012</v>
       </c>
       <c r="Q58">
-        <v>6.042356799999999</v>
+        <v>5.902309599999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2700907312536769</v>
+        <v>0.2753067947712043</v>
       </c>
       <c r="T58">
-        <v>1.371734191578299</v>
+        <v>1.403634986731283</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2261673717350803</v>
+        <v>0.2221995231081491</v>
       </c>
       <c r="W58">
-        <v>0.1135986298292902</v>
+        <v>0.1141811100077237</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9046694869403211</v>
+        <v>0.8887980924325962</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1834651544560204</v>
+        <v>0.1844751544560204</v>
       </c>
       <c r="C59">
-        <v>38.89603040006685</v>
+        <v>36.99985924955611</v>
       </c>
       <c r="D59">
-        <v>85.70003040006685</v>
+        <v>85.07585924955612</v>
       </c>
       <c r="E59">
-        <v>60.504</v>
+        <v>61.77600000000001</v>
       </c>
       <c r="F59">
-        <v>72.504</v>
+        <v>73.77600000000001</v>
       </c>
       <c r="G59">
         <v>25.7</v>
@@ -6125,37 +6125,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M59">
-        <v>10.6435872</v>
+        <v>10.8303168</v>
       </c>
       <c r="N59">
-        <v>-1.183587200000002</v>
+        <v>-1.370316800000001</v>
       </c>
       <c r="O59">
-        <v>-0.2958968000000004</v>
+        <v>-0.3425792000000003</v>
       </c>
       <c r="P59">
-        <v>-0.8876904000000012</v>
+        <v>-1.027737600000001</v>
       </c>
       <c r="Q59">
-        <v>5.902309599999999</v>
+        <v>5.762262399999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2753067947712043</v>
+        <v>0.2807712422657568</v>
       </c>
       <c r="T59">
-        <v>1.403634986731283</v>
+        <v>1.437054867367742</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2221995231081491</v>
+        <v>0.2183684968476637</v>
       </c>
       <c r="W59">
-        <v>0.1141811100077237</v>
+        <v>0.114743504662763</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8887980924325962</v>
+        <v>0.873473987390655</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1844751544560203</v>
+        <v>0.1854851544560204</v>
       </c>
       <c r="C60">
-        <v>36.99985924955615</v>
+        <v>35.11271429605924</v>
       </c>
       <c r="D60">
-        <v>85.07585924955615</v>
+        <v>84.46071429605924</v>
       </c>
       <c r="E60">
-        <v>61.776</v>
+        <v>63.048</v>
       </c>
       <c r="F60">
-        <v>73.776</v>
+        <v>75.048</v>
       </c>
       <c r="G60">
         <v>25.7</v>
@@ -6207,37 +6207,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M60">
-        <v>10.8303168</v>
+        <v>11.0170464</v>
       </c>
       <c r="N60">
-        <v>-1.370316799999999</v>
+        <v>-1.557046400000001</v>
       </c>
       <c r="O60">
-        <v>-0.3425791999999999</v>
+        <v>-0.3892616000000002</v>
       </c>
       <c r="P60">
-        <v>-1.0277376</v>
+        <v>-1.167784800000001</v>
       </c>
       <c r="Q60">
-        <v>5.762262400000001</v>
+        <v>5.622215199999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2807712422657567</v>
+        <v>0.2865022481746776</v>
       </c>
       <c r="T60">
-        <v>1.437054867367742</v>
+        <v>1.472104986084029</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2183684968476638</v>
+        <v>0.214667335884144</v>
       </c>
       <c r="W60">
-        <v>0.114743504662763</v>
+        <v>0.1152868350922077</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8734739873906552</v>
+        <v>0.8586693435365762</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1854851544560204</v>
+        <v>0.1864951544560204</v>
       </c>
       <c r="C61">
-        <v>35.11271429605924</v>
+        <v>33.2344011520932</v>
       </c>
       <c r="D61">
-        <v>84.46071429605924</v>
+        <v>83.85440115209319</v>
       </c>
       <c r="E61">
-        <v>63.048</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="F61">
-        <v>75.048</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="G61">
         <v>25.7</v>
@@ -6289,37 +6289,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M61">
-        <v>11.0170464</v>
+        <v>11.203776</v>
       </c>
       <c r="N61">
-        <v>-1.557046400000001</v>
+        <v>-1.743775999999999</v>
       </c>
       <c r="O61">
-        <v>-0.3892616000000002</v>
+        <v>-0.4359439999999997</v>
       </c>
       <c r="P61">
-        <v>-1.167784800000001</v>
+        <v>-1.307831999999999</v>
       </c>
       <c r="Q61">
-        <v>5.622215199999999</v>
+        <v>5.482168000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2865022481746776</v>
+        <v>0.2925198043790446</v>
       </c>
       <c r="T61">
-        <v>1.472104986084029</v>
+        <v>1.508907610736129</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.214667335884144</v>
+        <v>0.2110895469527417</v>
       </c>
       <c r="W61">
-        <v>0.1152868350922077</v>
+        <v>0.1158120545073375</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8586693435365762</v>
+        <v>0.8443581878109667</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1864951544560204</v>
+        <v>0.1875051544560204</v>
       </c>
       <c r="C62">
-        <v>33.2344011520932</v>
+        <v>31.36473097214289</v>
       </c>
       <c r="D62">
-        <v>83.85440115209319</v>
+        <v>83.25673097214289</v>
       </c>
       <c r="E62">
-        <v>64.31999999999999</v>
+        <v>65.592</v>
       </c>
       <c r="F62">
-        <v>76.31999999999999</v>
+        <v>77.592</v>
       </c>
       <c r="G62">
         <v>25.7</v>
@@ -6371,37 +6371,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M62">
-        <v>11.203776</v>
+        <v>11.3905056</v>
       </c>
       <c r="N62">
-        <v>-1.743775999999999</v>
+        <v>-1.9305056</v>
       </c>
       <c r="O62">
-        <v>-0.4359439999999997</v>
+        <v>-0.4826264</v>
       </c>
       <c r="P62">
-        <v>-1.307831999999999</v>
+        <v>-1.4478792</v>
       </c>
       <c r="Q62">
-        <v>5.482168000000001</v>
+        <v>5.3421208</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2925198043790446</v>
+        <v>0.2988459532092765</v>
       </c>
       <c r="T62">
-        <v>1.508907610736129</v>
+        <v>1.547597549472953</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2110895469527417</v>
+        <v>0.2076290625764672</v>
       </c>
       <c r="W62">
-        <v>0.1158120545073375</v>
+        <v>0.1163200536137746</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8443581878109667</v>
+        <v>0.8305162503058687</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1875051544560204</v>
+        <v>0.1885151544560204</v>
       </c>
       <c r="C63">
-        <v>31.36473097214289</v>
+        <v>29.50352025655783</v>
       </c>
       <c r="D63">
-        <v>83.25673097214289</v>
+        <v>82.66752025655784</v>
       </c>
       <c r="E63">
-        <v>65.592</v>
+        <v>66.864</v>
       </c>
       <c r="F63">
-        <v>77.592</v>
+        <v>78.864</v>
       </c>
       <c r="G63">
         <v>25.7</v>
@@ -6453,37 +6453,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M63">
-        <v>11.3905056</v>
+        <v>11.5772352</v>
       </c>
       <c r="N63">
-        <v>-1.9305056</v>
+        <v>-2.117235200000001</v>
       </c>
       <c r="O63">
-        <v>-0.4826264</v>
+        <v>-0.5293088000000004</v>
       </c>
       <c r="P63">
-        <v>-1.4478792</v>
+        <v>-1.587926400000001</v>
       </c>
       <c r="Q63">
-        <v>5.3421208</v>
+        <v>5.202073599999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2988459532092765</v>
+        <v>0.3055050572410996</v>
       </c>
       <c r="T63">
-        <v>1.547597549472953</v>
+        <v>1.588323800774873</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2076290625764672</v>
+        <v>0.2042802067284596</v>
       </c>
       <c r="W63">
-        <v>0.1163200536137746</v>
+        <v>0.1168116656522621</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8305162503058687</v>
+        <v>0.8171208269138386</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1885151544560204</v>
+        <v>0.1895251544560203</v>
       </c>
       <c r="C64">
-        <v>29.50352025655783</v>
+        <v>27.65059066371701</v>
       </c>
       <c r="D64">
-        <v>82.66752025655784</v>
+        <v>82.086590663717</v>
       </c>
       <c r="E64">
-        <v>66.864</v>
+        <v>68.136</v>
       </c>
       <c r="F64">
-        <v>78.864</v>
+        <v>80.136</v>
       </c>
       <c r="G64">
         <v>25.7</v>
@@ -6535,37 +6535,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M64">
-        <v>11.5772352</v>
+        <v>11.7639648</v>
       </c>
       <c r="N64">
-        <v>-2.117235200000001</v>
+        <v>-2.303964799999999</v>
       </c>
       <c r="O64">
-        <v>-0.5293088000000004</v>
+        <v>-0.5759911999999998</v>
       </c>
       <c r="P64">
-        <v>-1.587926400000001</v>
+        <v>-1.727973599999999</v>
       </c>
       <c r="Q64">
-        <v>5.202073599999999</v>
+        <v>5.062026400000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3055050572410996</v>
+        <v>0.3125241128422103</v>
       </c>
       <c r="T64">
-        <v>1.588323800774873</v>
+        <v>1.631251471066085</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2042802067284596</v>
+        <v>0.2010376637645159</v>
       </c>
       <c r="W64">
-        <v>0.1168116656522621</v>
+        <v>0.1172876709593691</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8171208269138386</v>
+        <v>0.8041506550580635</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1895251544560203</v>
+        <v>0.2289439563909335</v>
       </c>
       <c r="C65">
-        <v>27.65059066371701</v>
+        <v>8.710767369682628</v>
       </c>
       <c r="D65">
-        <v>82.086590663717</v>
+        <v>64.41876736968263</v>
       </c>
       <c r="E65">
-        <v>68.136</v>
+        <v>69.408</v>
       </c>
       <c r="F65">
-        <v>80.136</v>
+        <v>81.408</v>
       </c>
       <c r="G65">
         <v>25.7</v>
@@ -6617,45 +6617,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M65">
-        <v>11.7639648</v>
+        <v>16.3467264</v>
       </c>
       <c r="N65">
-        <v>-2.303964799999999</v>
+        <v>-6.886726400000001</v>
       </c>
       <c r="O65">
-        <v>-0.5759911999999998</v>
+        <v>-1.7216816</v>
       </c>
       <c r="P65">
-        <v>-1.727973599999999</v>
+        <v>-5.1650448</v>
       </c>
       <c r="Q65">
-        <v>5.062026400000001</v>
+        <v>1.6249552</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3125241128422103</v>
+        <v>0.330624232462586</v>
       </c>
       <c r="T65">
-        <v>1.631251471066085</v>
+        <v>1.741949549475955</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.2010376637645159</v>
+        <v>0.1446772853554336</v>
       </c>
       <c r="W65">
-        <v>0.1172876709593691</v>
+        <v>0.1717488011006289</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8041506550580635</v>
+        <v>0.5787091414217345</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2289439563909335</v>
+        <v>0.2304939563909335</v>
       </c>
       <c r="C66">
-        <v>8.710767369682628</v>
+        <v>6.898148221259248</v>
       </c>
       <c r="D66">
-        <v>64.41876736968263</v>
+        <v>63.87814822125925</v>
       </c>
       <c r="E66">
-        <v>69.408</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F66">
-        <v>81.408</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="G66">
         <v>25.7</v>
@@ -6699,37 +6699,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M66">
-        <v>16.3467264</v>
+        <v>16.602144</v>
       </c>
       <c r="N66">
-        <v>-6.886726400000001</v>
+        <v>-7.142144000000002</v>
       </c>
       <c r="O66">
-        <v>-1.7216816</v>
+        <v>-1.785536</v>
       </c>
       <c r="P66">
-        <v>-5.1650448</v>
+        <v>-5.356608000000001</v>
       </c>
       <c r="Q66">
-        <v>1.6249552</v>
+        <v>1.433391999999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.330624232462586</v>
+        <v>0.3387620676758027</v>
       </c>
       <c r="T66">
-        <v>1.741949549475955</v>
+        <v>1.79171953660384</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1446772853554336</v>
+        <v>0.14245148096535</v>
       </c>
       <c r="W66">
-        <v>0.1717488011006289</v>
+        <v>0.1721957426221577</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5787091414217345</v>
+        <v>0.5698059238614001</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2304939563909335</v>
+        <v>0.2320439563909334</v>
       </c>
       <c r="C67">
-        <v>6.898148221259248</v>
+        <v>5.09452758958021</v>
       </c>
       <c r="D67">
-        <v>63.87814822125925</v>
+        <v>63.34652758958022</v>
       </c>
       <c r="E67">
-        <v>70.68000000000001</v>
+        <v>71.95200000000001</v>
       </c>
       <c r="F67">
-        <v>82.68000000000001</v>
+        <v>83.95200000000001</v>
       </c>
       <c r="G67">
         <v>25.7</v>
@@ -6781,37 +6781,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M67">
-        <v>16.602144</v>
+        <v>16.8575616</v>
       </c>
       <c r="N67">
-        <v>-7.142144000000002</v>
+        <v>-7.397561600000003</v>
       </c>
       <c r="O67">
-        <v>-1.785536</v>
+        <v>-1.849390400000001</v>
       </c>
       <c r="P67">
-        <v>-5.356608000000001</v>
+        <v>-5.548171200000002</v>
       </c>
       <c r="Q67">
-        <v>1.433391999999999</v>
+        <v>1.241828799999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3387620676758027</v>
+        <v>0.3473785990780322</v>
       </c>
       <c r="T67">
-        <v>1.79171953660384</v>
+        <v>1.844417170033364</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.14245148096535</v>
+        <v>0.1402931251931477</v>
       </c>
       <c r="W67">
-        <v>0.1721957426221577</v>
+        <v>0.1726291404612159</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5698059238614001</v>
+        <v>0.561172500772591</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2320439563909334</v>
+        <v>0.2335939563909334</v>
       </c>
       <c r="C68">
-        <v>5.09452758958021</v>
+        <v>3.299682660750605</v>
       </c>
       <c r="D68">
-        <v>63.34652758958022</v>
+        <v>62.82368266075061</v>
       </c>
       <c r="E68">
-        <v>71.95200000000001</v>
+        <v>73.224</v>
       </c>
       <c r="F68">
-        <v>83.95200000000001</v>
+        <v>85.224</v>
       </c>
       <c r="G68">
         <v>25.7</v>
@@ -6863,37 +6863,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M68">
-        <v>16.8575616</v>
+        <v>17.1129792</v>
       </c>
       <c r="N68">
-        <v>-7.397561600000003</v>
+        <v>-7.652979200000001</v>
       </c>
       <c r="O68">
-        <v>-1.849390400000001</v>
+        <v>-1.9132448</v>
       </c>
       <c r="P68">
-        <v>-5.548171200000002</v>
+        <v>-5.739734400000001</v>
       </c>
       <c r="Q68">
-        <v>1.241828799999998</v>
+        <v>1.050265599999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3473785990780322</v>
+        <v>0.3565173445046392</v>
       </c>
       <c r="T68">
-        <v>1.844417170033364</v>
+        <v>1.900308599428315</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1402931251931477</v>
+        <v>0.138199197951459</v>
       </c>
       <c r="W68">
-        <v>0.1726291404612159</v>
+        <v>0.173049601051347</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.561172500772591</v>
+        <v>0.5527967918058359</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2335939563909334</v>
+        <v>0.2351439563909335</v>
       </c>
       <c r="C69">
-        <v>3.299682660750605</v>
+        <v>1.513397916836638</v>
       </c>
       <c r="D69">
-        <v>62.82368266075061</v>
+        <v>62.30939791683665</v>
       </c>
       <c r="E69">
-        <v>73.224</v>
+        <v>74.49600000000001</v>
       </c>
       <c r="F69">
-        <v>85.224</v>
+        <v>86.49600000000001</v>
       </c>
       <c r="G69">
         <v>25.7</v>
@@ -6945,37 +6945,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M69">
-        <v>17.1129792</v>
+        <v>17.3683968</v>
       </c>
       <c r="N69">
-        <v>-7.652979200000001</v>
+        <v>-7.908396800000002</v>
       </c>
       <c r="O69">
-        <v>-1.9132448</v>
+        <v>-1.977099200000001</v>
       </c>
       <c r="P69">
-        <v>-5.739734400000001</v>
+        <v>-5.931297600000002</v>
       </c>
       <c r="Q69">
-        <v>1.050265599999999</v>
+        <v>0.8587023999999985</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3565173445046392</v>
+        <v>0.3662272615204092</v>
       </c>
       <c r="T69">
-        <v>1.900308599428315</v>
+        <v>1.959693243160449</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.138199197951459</v>
+        <v>0.136166856805114</v>
       </c>
       <c r="W69">
-        <v>0.173049601051347</v>
+        <v>0.1734576951535331</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5527967918058359</v>
+        <v>0.5446674272204559</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2351439563909335</v>
+        <v>0.2366939563909335</v>
       </c>
       <c r="C70">
-        <v>1.513397916836638</v>
+        <v>-0.2645351603389798</v>
       </c>
       <c r="D70">
-        <v>62.30939791683665</v>
+        <v>61.80346483966103</v>
       </c>
       <c r="E70">
-        <v>74.49600000000001</v>
+        <v>75.76800000000001</v>
       </c>
       <c r="F70">
-        <v>86.49600000000001</v>
+        <v>87.76800000000001</v>
       </c>
       <c r="G70">
         <v>25.7</v>
@@ -7027,37 +7027,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M70">
-        <v>17.3683968</v>
+        <v>17.6238144</v>
       </c>
       <c r="N70">
-        <v>-7.908396800000002</v>
+        <v>-8.163814400000003</v>
       </c>
       <c r="O70">
-        <v>-1.977099200000001</v>
+        <v>-2.040953600000001</v>
       </c>
       <c r="P70">
-        <v>-5.931297600000002</v>
+        <v>-6.122860800000002</v>
       </c>
       <c r="Q70">
-        <v>0.8587023999999985</v>
+        <v>0.6671391999999976</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3662272615204092</v>
+        <v>0.3765636247952611</v>
       </c>
       <c r="T70">
-        <v>1.959693243160449</v>
+        <v>2.022909154230141</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.136166856805114</v>
+        <v>0.1341934240977935</v>
       </c>
       <c r="W70">
-        <v>0.1734576951535331</v>
+        <v>0.1738539604411631</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5446674272204559</v>
+        <v>0.5367736963911739</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2366939563909335</v>
+        <v>0.2382439563909334</v>
       </c>
       <c r="C71">
-        <v>-0.2645351603389798</v>
+        <v>-2.034318371087735</v>
       </c>
       <c r="D71">
-        <v>61.80346483966103</v>
+        <v>61.30568162891227</v>
       </c>
       <c r="E71">
-        <v>75.76800000000001</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="F71">
-        <v>87.76800000000001</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="G71">
         <v>25.7</v>
@@ -7109,37 +7109,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M71">
-        <v>17.6238144</v>
+        <v>17.879232</v>
       </c>
       <c r="N71">
-        <v>-8.163814400000003</v>
+        <v>-8.419232000000001</v>
       </c>
       <c r="O71">
-        <v>-2.040953600000001</v>
+        <v>-2.104808</v>
       </c>
       <c r="P71">
-        <v>-6.122860800000002</v>
+        <v>-6.314424000000001</v>
       </c>
       <c r="Q71">
-        <v>0.6671391999999976</v>
+        <v>0.4755759999999993</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3765636247952611</v>
+        <v>0.3875890789551032</v>
       </c>
       <c r="T71">
-        <v>2.022909154230141</v>
+        <v>2.090339459371146</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1341934240977935</v>
+        <v>0.1322763751821107</v>
       </c>
       <c r="W71">
-        <v>0.1738539604411631</v>
+        <v>0.1742389038634322</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5367736963911739</v>
+        <v>0.5291055007284429</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2382439563909334</v>
+        <v>0.2397939563909335</v>
       </c>
       <c r="C72">
-        <v>-2.034318371087735</v>
+        <v>-3.796147066231867</v>
       </c>
       <c r="D72">
-        <v>61.30568162891227</v>
+        <v>60.81585293376814</v>
       </c>
       <c r="E72">
-        <v>77.04000000000001</v>
+        <v>78.31200000000001</v>
       </c>
       <c r="F72">
-        <v>89.04000000000001</v>
+        <v>90.31200000000001</v>
       </c>
       <c r="G72">
         <v>25.7</v>
@@ -7191,37 +7191,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M72">
-        <v>17.879232</v>
+        <v>18.1346496</v>
       </c>
       <c r="N72">
-        <v>-8.419232000000001</v>
+        <v>-8.674649600000002</v>
       </c>
       <c r="O72">
-        <v>-2.104808</v>
+        <v>-2.168662400000001</v>
       </c>
       <c r="P72">
-        <v>-6.314424000000001</v>
+        <v>-6.505987200000002</v>
       </c>
       <c r="Q72">
-        <v>0.4755759999999993</v>
+        <v>0.2840127999999984</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3875890789551032</v>
+        <v>0.3993749092638999</v>
       </c>
       <c r="T72">
-        <v>2.090339459371146</v>
+        <v>2.162420130383945</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1322763751821107</v>
+        <v>0.1304133276443345</v>
       </c>
       <c r="W72">
-        <v>0.1742389038634322</v>
+        <v>0.1746130038090176</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5291055007284429</v>
+        <v>0.521653310577338</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2397939563909335</v>
+        <v>0.2413439563909335</v>
       </c>
       <c r="C73">
-        <v>-3.796147066231839</v>
+        <v>-5.550210402717099</v>
       </c>
       <c r="D73">
-        <v>60.81585293376816</v>
+        <v>60.3337895972829</v>
       </c>
       <c r="E73">
-        <v>78.312</v>
+        <v>79.584</v>
       </c>
       <c r="F73">
-        <v>90.312</v>
+        <v>91.584</v>
       </c>
       <c r="G73">
         <v>25.7</v>
@@ -7273,37 +7273,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M73">
-        <v>18.1346496</v>
+        <v>18.3900672</v>
       </c>
       <c r="N73">
-        <v>-8.674649599999999</v>
+        <v>-8.9300672</v>
       </c>
       <c r="O73">
-        <v>-2.1686624</v>
+        <v>-2.2325168</v>
       </c>
       <c r="P73">
-        <v>-6.505987199999999</v>
+        <v>-6.6975504</v>
       </c>
       <c r="Q73">
-        <v>0.2840128000000011</v>
+        <v>0.09244960000000013</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3993749092638998</v>
+        <v>0.4120025845947533</v>
       </c>
       <c r="T73">
-        <v>2.162420130383944</v>
+        <v>2.239649420754799</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1304133276443345</v>
+        <v>0.1286020314270521</v>
       </c>
       <c r="W73">
-        <v>0.1746130038090176</v>
+        <v>0.174976712089448</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5216533105773382</v>
+        <v>0.5144081257082085</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2413439563909335</v>
+        <v>0.2428939563909335</v>
       </c>
       <c r="C74">
-        <v>-5.550210402717099</v>
+        <v>-7.29669158716446</v>
       </c>
       <c r="D74">
-        <v>60.3337895972829</v>
+        <v>59.85930841283553</v>
       </c>
       <c r="E74">
-        <v>79.584</v>
+        <v>80.85599999999999</v>
       </c>
       <c r="F74">
-        <v>91.584</v>
+        <v>92.85599999999999</v>
       </c>
       <c r="G74">
         <v>25.7</v>
@@ -7355,37 +7355,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M74">
-        <v>18.3900672</v>
+        <v>18.6454848</v>
       </c>
       <c r="N74">
-        <v>-8.9300672</v>
+        <v>-9.185484799999998</v>
       </c>
       <c r="O74">
-        <v>-2.2325168</v>
+        <v>-2.296371199999999</v>
       </c>
       <c r="P74">
-        <v>-6.6975504</v>
+        <v>-6.889113599999998</v>
       </c>
       <c r="Q74">
-        <v>0.09244960000000013</v>
+        <v>-0.09911359999999814</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4120025845947533</v>
+        <v>0.4255656432834479</v>
       </c>
       <c r="T74">
-        <v>2.239649420754799</v>
+        <v>2.322599399301273</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1286020314270521</v>
+        <v>0.1268403597636678</v>
       </c>
       <c r="W74">
-        <v>0.174976712089448</v>
+        <v>0.1753304557594555</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5144081257082085</v>
+        <v>0.5073614390546715</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2428939563909335</v>
+        <v>0.2444439563909335</v>
       </c>
       <c r="C75">
-        <v>-7.29669158716446</v>
+        <v>-9.035768108019198</v>
       </c>
       <c r="D75">
-        <v>59.85930841283553</v>
+        <v>59.39223189198081</v>
       </c>
       <c r="E75">
-        <v>80.85599999999999</v>
+        <v>82.128</v>
       </c>
       <c r="F75">
-        <v>92.85599999999999</v>
+        <v>94.128</v>
       </c>
       <c r="G75">
         <v>25.7</v>
@@ -7437,37 +7437,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M75">
-        <v>18.6454848</v>
+        <v>18.9009024</v>
       </c>
       <c r="N75">
-        <v>-9.185484799999998</v>
+        <v>-9.440902399999999</v>
       </c>
       <c r="O75">
-        <v>-2.296371199999999</v>
+        <v>-2.3602256</v>
       </c>
       <c r="P75">
-        <v>-6.889113599999998</v>
+        <v>-7.080676799999999</v>
       </c>
       <c r="Q75">
-        <v>-0.09911359999999814</v>
+        <v>-0.2906767999999991</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4255656432834479</v>
+        <v>0.4401720141789651</v>
       </c>
       <c r="T75">
-        <v>2.322599399301273</v>
+        <v>2.411930145428245</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1268403597636678</v>
+        <v>0.1251263008479426</v>
       </c>
       <c r="W75">
-        <v>0.1753304557594555</v>
+        <v>0.1756746387897331</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5073614390546715</v>
+        <v>0.5005052033917704</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2444439563909335</v>
+        <v>0.2737969944600429</v>
       </c>
       <c r="C76">
-        <v>-9.035768108019198</v>
+        <v>-17.95410769185179</v>
       </c>
       <c r="D76">
-        <v>59.39223189198081</v>
+        <v>51.74589230814821</v>
       </c>
       <c r="E76">
-        <v>82.128</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F76">
-        <v>94.128</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="G76">
         <v>25.7</v>
@@ -7519,45 +7519,45 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M76">
-        <v>18.9009024</v>
+        <v>22.49532</v>
       </c>
       <c r="N76">
-        <v>-9.440902399999999</v>
+        <v>-13.03532</v>
       </c>
       <c r="O76">
-        <v>-2.3602256</v>
+        <v>-3.258830000000001</v>
       </c>
       <c r="P76">
-        <v>-7.080676799999999</v>
+        <v>-9.776490000000003</v>
       </c>
       <c r="Q76">
-        <v>-0.2906767999999991</v>
+        <v>-2.986490000000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4401720141789651</v>
+        <v>0.4621590470225613</v>
       </c>
       <c r="T76">
-        <v>2.411930145428245</v>
+        <v>2.546400101250022</v>
       </c>
       <c r="U76">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1251263008479426</v>
+        <v>0.1051329787706954</v>
       </c>
       <c r="W76">
-        <v>0.1756746387897331</v>
+        <v>0.21100964360587</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.5005052033917704</v>
+        <v>0.4205319150827816</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2737969944600429</v>
+        <v>0.2756969944600428</v>
       </c>
       <c r="C77">
-        <v>-17.95410769185179</v>
+        <v>-19.65376528527268</v>
       </c>
       <c r="D77">
-        <v>51.74589230814821</v>
+        <v>51.31823471472732</v>
       </c>
       <c r="E77">
-        <v>83.40000000000001</v>
+        <v>84.672</v>
       </c>
       <c r="F77">
-        <v>95.40000000000001</v>
+        <v>96.672</v>
       </c>
       <c r="G77">
         <v>25.7</v>
@@ -7601,37 +7601,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M77">
-        <v>22.49532</v>
+        <v>22.7952576</v>
       </c>
       <c r="N77">
-        <v>-13.03532</v>
+        <v>-13.3352576</v>
       </c>
       <c r="O77">
-        <v>-3.258830000000001</v>
+        <v>-3.3338144</v>
       </c>
       <c r="P77">
-        <v>-9.776490000000003</v>
+        <v>-10.0014432</v>
       </c>
       <c r="Q77">
-        <v>-2.986490000000003</v>
+        <v>-3.211443199999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4621590470225613</v>
+        <v>0.4795073406485014</v>
       </c>
       <c r="T77">
-        <v>2.546400101250022</v>
+        <v>2.652500105468773</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1051329787706954</v>
+        <v>0.10374965010266</v>
       </c>
       <c r="W77">
-        <v>0.21100964360587</v>
+        <v>0.2113358325057928</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4205319150827816</v>
+        <v>0.4149986004106399</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2756969944600428</v>
+        <v>0.2775969944600428</v>
       </c>
       <c r="C78">
-        <v>-19.65376528527268</v>
+        <v>-21.34641200756998</v>
       </c>
       <c r="D78">
-        <v>51.31823471472732</v>
+        <v>50.89758799243002</v>
       </c>
       <c r="E78">
-        <v>84.672</v>
+        <v>85.944</v>
       </c>
       <c r="F78">
-        <v>96.672</v>
+        <v>97.944</v>
       </c>
       <c r="G78">
         <v>25.7</v>
@@ -7683,37 +7683,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M78">
-        <v>22.7952576</v>
+        <v>23.0951952</v>
       </c>
       <c r="N78">
-        <v>-13.3352576</v>
+        <v>-13.6351952</v>
       </c>
       <c r="O78">
-        <v>-3.3338144</v>
+        <v>-3.4087988</v>
       </c>
       <c r="P78">
-        <v>-10.0014432</v>
+        <v>-10.2263964</v>
       </c>
       <c r="Q78">
-        <v>-3.211443199999999</v>
+        <v>-3.436396400000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4795073406485014</v>
+        <v>0.4983641815462623</v>
       </c>
       <c r="T78">
-        <v>2.652500105468773</v>
+        <v>2.767826197010893</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.10374965010266</v>
+        <v>0.1024022520493787</v>
       </c>
       <c r="W78">
-        <v>0.2113358325057928</v>
+        <v>0.2116535489667565</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4149986004106399</v>
+        <v>0.4096090081975146</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2775969944600428</v>
+        <v>0.2794969944600428</v>
       </c>
       <c r="C79">
-        <v>-21.34641200756998</v>
+        <v>-23.03221885779952</v>
       </c>
       <c r="D79">
-        <v>50.89758799243002</v>
+        <v>50.48378114220049</v>
       </c>
       <c r="E79">
-        <v>85.944</v>
+        <v>87.21600000000001</v>
       </c>
       <c r="F79">
-        <v>97.944</v>
+        <v>99.21600000000001</v>
       </c>
       <c r="G79">
         <v>25.7</v>
@@ -7765,37 +7765,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M79">
-        <v>23.0951952</v>
+        <v>23.3951328</v>
       </c>
       <c r="N79">
-        <v>-13.6351952</v>
+        <v>-13.9351328</v>
       </c>
       <c r="O79">
-        <v>-3.4087988</v>
+        <v>-3.4837832</v>
       </c>
       <c r="P79">
-        <v>-10.2263964</v>
+        <v>-10.4513496</v>
       </c>
       <c r="Q79">
-        <v>-3.436396400000002</v>
+        <v>-3.6613496</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4983641815462623</v>
+        <v>0.518935280707456</v>
       </c>
       <c r="T79">
-        <v>2.767826197010893</v>
+        <v>2.893636478693206</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1024022520493787</v>
+        <v>0.1010894026641302</v>
       </c>
       <c r="W79">
-        <v>0.2116535489667565</v>
+        <v>0.2119631188517981</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4096090081975146</v>
+        <v>0.4043576106565209</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2794969944600428</v>
+        <v>0.2813969944600429</v>
       </c>
       <c r="C80">
-        <v>-23.03221885779952</v>
+        <v>-24.71135131884819</v>
       </c>
       <c r="D80">
-        <v>50.48378114220049</v>
+        <v>50.07664868115182</v>
       </c>
       <c r="E80">
-        <v>87.21600000000001</v>
+        <v>88.48800000000001</v>
       </c>
       <c r="F80">
-        <v>99.21600000000001</v>
+        <v>100.488</v>
       </c>
       <c r="G80">
         <v>25.7</v>
@@ -7847,37 +7847,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M80">
-        <v>23.3951328</v>
+        <v>23.69507040000001</v>
       </c>
       <c r="N80">
-        <v>-13.9351328</v>
+        <v>-14.23507040000001</v>
       </c>
       <c r="O80">
-        <v>-3.4837832</v>
+        <v>-3.558767600000001</v>
       </c>
       <c r="P80">
-        <v>-10.4513496</v>
+        <v>-10.6763028</v>
       </c>
       <c r="Q80">
-        <v>-3.6613496</v>
+        <v>-3.886302800000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.518935280707456</v>
+        <v>0.5414655321697159</v>
       </c>
       <c r="T80">
-        <v>2.893636478693206</v>
+        <v>3.031428691964312</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1010894026641302</v>
+        <v>0.09980978997217918</v>
       </c>
       <c r="W80">
-        <v>0.2119631188517981</v>
+        <v>0.2122648515245602</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4043576106565209</v>
+        <v>0.3992391598887167</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2813969944600429</v>
+        <v>0.2832969944600428</v>
       </c>
       <c r="C81">
-        <v>-24.71135131884819</v>
+        <v>-26.38396957808341</v>
       </c>
       <c r="D81">
-        <v>50.07664868115182</v>
+        <v>49.67603042191659</v>
       </c>
       <c r="E81">
-        <v>88.48800000000001</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F81">
-        <v>100.488</v>
+        <v>101.76</v>
       </c>
       <c r="G81">
         <v>25.7</v>
@@ -7929,37 +7929,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M81">
-        <v>23.69507040000001</v>
+        <v>23.995008</v>
       </c>
       <c r="N81">
-        <v>-14.23507040000001</v>
+        <v>-14.535008</v>
       </c>
       <c r="O81">
-        <v>-3.558767600000001</v>
+        <v>-3.633752</v>
       </c>
       <c r="P81">
-        <v>-10.6763028</v>
+        <v>-10.901256</v>
       </c>
       <c r="Q81">
-        <v>-3.886302800000004</v>
+        <v>-4.111256</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5414655321697159</v>
+        <v>0.5662488087782016</v>
       </c>
       <c r="T81">
-        <v>3.031428691964312</v>
+        <v>3.183000126562527</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09980978997217918</v>
+        <v>0.09856216759752695</v>
       </c>
       <c r="W81">
-        <v>0.2122648515245602</v>
+        <v>0.2125590408805031</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3992391598887167</v>
+        <v>0.3942486703901078</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2832969944600428</v>
+        <v>0.2851969944600429</v>
       </c>
       <c r="C82">
-        <v>-26.38396957808341</v>
+        <v>-28.05022873749571</v>
       </c>
       <c r="D82">
-        <v>49.67603042191659</v>
+        <v>49.2817712625043</v>
       </c>
       <c r="E82">
-        <v>89.76000000000001</v>
+        <v>91.03200000000001</v>
       </c>
       <c r="F82">
-        <v>101.76</v>
+        <v>103.032</v>
       </c>
       <c r="G82">
         <v>25.7</v>
@@ -8011,37 +8011,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M82">
-        <v>23.995008</v>
+        <v>24.2949456</v>
       </c>
       <c r="N82">
-        <v>-14.535008</v>
+        <v>-14.8349456</v>
       </c>
       <c r="O82">
-        <v>-3.633752</v>
+        <v>-3.7087364</v>
       </c>
       <c r="P82">
-        <v>-10.901256</v>
+        <v>-11.1262092</v>
       </c>
       <c r="Q82">
-        <v>-4.111256</v>
+        <v>-4.336209200000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5662488087782016</v>
+        <v>0.5936408513454754</v>
       </c>
       <c r="T82">
-        <v>3.183000126562527</v>
+        <v>3.350526449013187</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09856216759752695</v>
+        <v>0.09734535071360687</v>
       </c>
       <c r="W82">
-        <v>0.2125590408805031</v>
+        <v>0.2128459663017315</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3942486703901078</v>
+        <v>0.3893814028544275</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2851969944600429</v>
+        <v>0.2870969944600428</v>
       </c>
       <c r="C83">
-        <v>-28.05022873749571</v>
+        <v>-29.71027901391248</v>
       </c>
       <c r="D83">
-        <v>49.2817712625043</v>
+        <v>48.89372098608753</v>
       </c>
       <c r="E83">
-        <v>91.03200000000001</v>
+        <v>92.30400000000002</v>
       </c>
       <c r="F83">
-        <v>103.032</v>
+        <v>104.304</v>
       </c>
       <c r="G83">
         <v>25.7</v>
@@ -8093,37 +8093,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M83">
-        <v>24.2949456</v>
+        <v>24.59488320000001</v>
       </c>
       <c r="N83">
-        <v>-14.8349456</v>
+        <v>-15.1348832</v>
       </c>
       <c r="O83">
-        <v>-3.7087364</v>
+        <v>-3.783720800000001</v>
       </c>
       <c r="P83">
-        <v>-11.1262092</v>
+        <v>-11.3511624</v>
       </c>
       <c r="Q83">
-        <v>-4.336209200000002</v>
+        <v>-4.561162400000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5936408513454754</v>
+        <v>0.6240764541980018</v>
       </c>
       <c r="T83">
-        <v>3.350526449013187</v>
+        <v>3.536666807291697</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09734535071360687</v>
+        <v>0.09615821229027019</v>
       </c>
       <c r="W83">
-        <v>0.2128459663017315</v>
+        <v>0.2131258935419543</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3893814028544275</v>
+        <v>0.3846328491610808</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2870969944600428</v>
+        <v>0.2889969944600428</v>
       </c>
       <c r="C84">
-        <v>-29.71027901391248</v>
+        <v>-31.36426592982738</v>
       </c>
       <c r="D84">
-        <v>48.89372098608753</v>
+        <v>48.51173407017262</v>
       </c>
       <c r="E84">
-        <v>92.30400000000002</v>
+        <v>93.57600000000001</v>
       </c>
       <c r="F84">
-        <v>104.304</v>
+        <v>105.576</v>
       </c>
       <c r="G84">
         <v>25.7</v>
@@ -8175,37 +8175,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M84">
-        <v>24.59488320000001</v>
+        <v>24.8948208</v>
       </c>
       <c r="N84">
-        <v>-15.1348832</v>
+        <v>-15.4348208</v>
       </c>
       <c r="O84">
-        <v>-3.783720800000001</v>
+        <v>-3.8587052</v>
       </c>
       <c r="P84">
-        <v>-11.3511624</v>
+        <v>-11.5761156</v>
       </c>
       <c r="Q84">
-        <v>-4.561162400000003</v>
+        <v>-4.786115600000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6240764541980018</v>
+        <v>0.6580927162096492</v>
       </c>
       <c r="T84">
-        <v>3.536666807291697</v>
+        <v>3.744706031250034</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09615821229027019</v>
+        <v>0.09499967961207417</v>
       </c>
       <c r="W84">
-        <v>0.2131258935419543</v>
+        <v>0.2133990755474729</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3846328491610808</v>
+        <v>0.3799987184482967</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2889969944600428</v>
+        <v>0.2908969944600429</v>
       </c>
       <c r="C85">
-        <v>-31.36426592982738</v>
+        <v>-33.01233049535332</v>
       </c>
       <c r="D85">
-        <v>48.51173407017262</v>
+        <v>48.13566950464669</v>
       </c>
       <c r="E85">
-        <v>93.57600000000001</v>
+        <v>94.84800000000001</v>
       </c>
       <c r="F85">
-        <v>105.576</v>
+        <v>106.848</v>
       </c>
       <c r="G85">
         <v>25.7</v>
@@ -8257,37 +8257,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M85">
-        <v>24.8948208</v>
+        <v>25.1947584</v>
       </c>
       <c r="N85">
-        <v>-15.4348208</v>
+        <v>-15.7347584</v>
       </c>
       <c r="O85">
-        <v>-3.8587052</v>
+        <v>-3.933689600000001</v>
       </c>
       <c r="P85">
-        <v>-11.5761156</v>
+        <v>-11.8010688</v>
       </c>
       <c r="Q85">
-        <v>-4.786115600000001</v>
+        <v>-5.011068800000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6580927162096492</v>
+        <v>0.6963610109727523</v>
       </c>
       <c r="T85">
-        <v>3.744706031250034</v>
+        <v>3.978750158203161</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09499967961207417</v>
+        <v>0.09386873104526375</v>
       </c>
       <c r="W85">
-        <v>0.2133990755474729</v>
+        <v>0.2136657532195268</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3799987184482967</v>
+        <v>0.375474924181055</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2908969944600429</v>
+        <v>0.2927969944600428</v>
       </c>
       <c r="C86">
-        <v>-33.01233049535331</v>
+        <v>-34.65460938177768</v>
       </c>
       <c r="D86">
-        <v>48.13566950464669</v>
+        <v>47.76539061822233</v>
       </c>
       <c r="E86">
-        <v>94.848</v>
+        <v>96.12</v>
       </c>
       <c r="F86">
-        <v>106.848</v>
+        <v>108.12</v>
       </c>
       <c r="G86">
         <v>25.7</v>
@@ -8339,37 +8339,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M86">
-        <v>25.1947584</v>
+        <v>25.494696</v>
       </c>
       <c r="N86">
-        <v>-15.7347584</v>
+        <v>-16.034696</v>
       </c>
       <c r="O86">
-        <v>-3.9336896</v>
+        <v>-4.008674</v>
       </c>
       <c r="P86">
-        <v>-11.8010688</v>
+        <v>-12.026022</v>
       </c>
       <c r="Q86">
-        <v>-5.011068799999999</v>
+        <v>-5.236022000000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6963610109727518</v>
+        <v>0.7397317450376021</v>
       </c>
       <c r="T86">
-        <v>3.978750158203158</v>
+        <v>4.244000168750036</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09386873104526376</v>
+        <v>0.09276439303296655</v>
       </c>
       <c r="W86">
-        <v>0.2136657532195268</v>
+        <v>0.2139261561228265</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3754749241810551</v>
+        <v>0.3710575721318662</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2927969944600428</v>
+        <v>0.2946969944600428</v>
       </c>
       <c r="C87">
-        <v>-34.65460938177768</v>
+        <v>-36.29123508716837</v>
       </c>
       <c r="D87">
-        <v>47.76539061822233</v>
+        <v>47.40076491283162</v>
       </c>
       <c r="E87">
-        <v>96.12</v>
+        <v>97.392</v>
       </c>
       <c r="F87">
-        <v>108.12</v>
+        <v>109.392</v>
       </c>
       <c r="G87">
         <v>25.7</v>
@@ -8421,37 +8421,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M87">
-        <v>25.494696</v>
+        <v>25.7946336</v>
       </c>
       <c r="N87">
-        <v>-16.034696</v>
+        <v>-16.3346336</v>
       </c>
       <c r="O87">
-        <v>-4.008674</v>
+        <v>-4.0836584</v>
       </c>
       <c r="P87">
-        <v>-12.026022</v>
+        <v>-12.2509752</v>
       </c>
       <c r="Q87">
-        <v>-5.236022000000001</v>
+        <v>-5.460975199999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7397317450376021</v>
+        <v>0.7892982982545735</v>
       </c>
       <c r="T87">
-        <v>4.244000168750036</v>
+        <v>4.547143037946467</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09276439303296655</v>
+        <v>0.09168573730002508</v>
       </c>
       <c r="W87">
-        <v>0.2139261561228265</v>
+        <v>0.2141805031446541</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3710575721318662</v>
+        <v>0.3667429492001003</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2946969944600428</v>
+        <v>0.2965969944600428</v>
       </c>
       <c r="C88">
-        <v>-36.29123508716837</v>
+        <v>-37.92233609445231</v>
       </c>
       <c r="D88">
-        <v>47.40076491283162</v>
+        <v>47.0416639055477</v>
       </c>
       <c r="E88">
-        <v>97.392</v>
+        <v>98.664</v>
       </c>
       <c r="F88">
-        <v>109.392</v>
+        <v>110.664</v>
       </c>
       <c r="G88">
         <v>25.7</v>
@@ -8503,37 +8503,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M88">
-        <v>25.7946336</v>
+        <v>26.0945712</v>
       </c>
       <c r="N88">
-        <v>-16.3346336</v>
+        <v>-16.6345712</v>
       </c>
       <c r="O88">
-        <v>-4.0836584</v>
+        <v>-4.1586428</v>
       </c>
       <c r="P88">
-        <v>-12.2509752</v>
+        <v>-12.4759284</v>
       </c>
       <c r="Q88">
-        <v>-5.460975199999999</v>
+        <v>-5.685928400000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7892982982545735</v>
+        <v>0.846490475043387</v>
       </c>
       <c r="T88">
-        <v>4.547143037946467</v>
+        <v>4.896923271634657</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09168573730002508</v>
+        <v>0.0906318782505995</v>
       </c>
       <c r="W88">
-        <v>0.2141805031446541</v>
+        <v>0.2144290031085087</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3667429492001003</v>
+        <v>0.362527513002398</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2965969944600428</v>
+        <v>0.2984969944600429</v>
       </c>
       <c r="C89">
-        <v>-37.92233609445231</v>
+        <v>-39.54803702236214</v>
       </c>
       <c r="D89">
-        <v>47.0416639055477</v>
+        <v>46.68796297763787</v>
       </c>
       <c r="E89">
-        <v>98.664</v>
+        <v>99.93600000000001</v>
       </c>
       <c r="F89">
-        <v>110.664</v>
+        <v>111.936</v>
       </c>
       <c r="G89">
         <v>25.7</v>
@@ -8585,37 +8585,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M89">
-        <v>26.0945712</v>
+        <v>26.3945088</v>
       </c>
       <c r="N89">
-        <v>-16.6345712</v>
+        <v>-16.9345088</v>
       </c>
       <c r="O89">
-        <v>-4.1586428</v>
+        <v>-4.233627200000001</v>
       </c>
       <c r="P89">
-        <v>-12.4759284</v>
+        <v>-12.7008816</v>
       </c>
       <c r="Q89">
-        <v>-5.685928400000001</v>
+        <v>-5.910881600000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.846490475043387</v>
+        <v>0.9132146812970028</v>
       </c>
       <c r="T89">
-        <v>4.896923271634657</v>
+        <v>5.305000210937546</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0906318782505995</v>
+        <v>0.08960197054320632</v>
       </c>
       <c r="W89">
-        <v>0.2144290031085087</v>
+        <v>0.214671855345912</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.362527513002398</v>
+        <v>0.3584078821728253</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2984969944600429</v>
+        <v>0.3003969944600428</v>
       </c>
       <c r="C90">
-        <v>-39.54803702236214</v>
+        <v>-41.16845876962448</v>
       </c>
       <c r="D90">
-        <v>46.68796297763787</v>
+        <v>46.33954123037552</v>
       </c>
       <c r="E90">
-        <v>99.93600000000001</v>
+        <v>101.208</v>
       </c>
       <c r="F90">
-        <v>111.936</v>
+        <v>113.208</v>
       </c>
       <c r="G90">
         <v>25.7</v>
@@ -8667,37 +8667,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M90">
-        <v>26.3945088</v>
+        <v>26.6944464</v>
       </c>
       <c r="N90">
-        <v>-16.9345088</v>
+        <v>-17.2344464</v>
       </c>
       <c r="O90">
-        <v>-4.233627200000001</v>
+        <v>-4.3086116</v>
       </c>
       <c r="P90">
-        <v>-12.7008816</v>
+        <v>-12.9258348</v>
       </c>
       <c r="Q90">
-        <v>-5.910881600000002</v>
+        <v>-6.1358348</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9132146812970028</v>
+        <v>0.992070561414912</v>
       </c>
       <c r="T90">
-        <v>5.305000210937546</v>
+        <v>5.787272957386413</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08960197054320632</v>
+        <v>0.08859520682923772</v>
       </c>
       <c r="W90">
-        <v>0.214671855345912</v>
+        <v>0.2149092502296658</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3584078821728253</v>
+        <v>0.3543808273169509</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3003969944600428</v>
+        <v>0.3022969944600428</v>
       </c>
       <c r="C91">
-        <v>-41.16845876962448</v>
+        <v>-42.78371865273952</v>
       </c>
       <c r="D91">
-        <v>46.33954123037552</v>
+        <v>45.99628134726049</v>
       </c>
       <c r="E91">
-        <v>101.208</v>
+        <v>102.48</v>
       </c>
       <c r="F91">
-        <v>113.208</v>
+        <v>114.48</v>
       </c>
       <c r="G91">
         <v>25.7</v>
@@ -8749,37 +8749,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M91">
-        <v>26.6944464</v>
+        <v>26.994384</v>
       </c>
       <c r="N91">
-        <v>-17.2344464</v>
+        <v>-17.534384</v>
       </c>
       <c r="O91">
-        <v>-4.3086116</v>
+        <v>-4.383596000000001</v>
       </c>
       <c r="P91">
-        <v>-12.9258348</v>
+        <v>-13.150788</v>
       </c>
       <c r="Q91">
-        <v>-6.1358348</v>
+        <v>-6.360788000000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.992070561414912</v>
+        <v>1.086697617556403</v>
       </c>
       <c r="T91">
-        <v>5.787272957386413</v>
+        <v>6.366000253125055</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08859520682923772</v>
+        <v>0.08761081564224618</v>
       </c>
       <c r="W91">
-        <v>0.2149092502296658</v>
+        <v>0.2151413696715584</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3543808273169509</v>
+        <v>0.3504432625689847</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3022969944600428</v>
+        <v>0.3041969944600428</v>
       </c>
       <c r="C92">
-        <v>-42.78371865273952</v>
+        <v>-44.39393053768198</v>
       </c>
       <c r="D92">
-        <v>45.99628134726049</v>
+        <v>45.65806946231803</v>
       </c>
       <c r="E92">
-        <v>102.48</v>
+        <v>103.752</v>
       </c>
       <c r="F92">
-        <v>114.48</v>
+        <v>115.752</v>
       </c>
       <c r="G92">
         <v>25.7</v>
@@ -8831,37 +8831,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M92">
-        <v>26.994384</v>
+        <v>27.2943216</v>
       </c>
       <c r="N92">
-        <v>-17.534384</v>
+        <v>-17.8343216</v>
       </c>
       <c r="O92">
-        <v>-4.383596000000001</v>
+        <v>-4.458580400000001</v>
       </c>
       <c r="P92">
-        <v>-13.150788</v>
+        <v>-13.3757412</v>
       </c>
       <c r="Q92">
-        <v>-6.360788000000002</v>
+        <v>-6.585741200000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.086697617556403</v>
+        <v>1.202352908396004</v>
       </c>
       <c r="T92">
-        <v>6.366000253125055</v>
+        <v>7.073333614583396</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08761081564224618</v>
+        <v>0.08664805942639732</v>
       </c>
       <c r="W92">
-        <v>0.2151413696715584</v>
+        <v>0.2153683875872555</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3504432625689847</v>
+        <v>0.3465922377055892</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3041969944600428</v>
+        <v>0.3060969944600428</v>
       </c>
       <c r="C93">
-        <v>-44.39393053768198</v>
+        <v>-45.99920496583417</v>
       </c>
       <c r="D93">
-        <v>45.65806946231803</v>
+        <v>45.32479503416584</v>
       </c>
       <c r="E93">
-        <v>103.752</v>
+        <v>105.024</v>
       </c>
       <c r="F93">
-        <v>115.752</v>
+        <v>117.024</v>
       </c>
       <c r="G93">
         <v>25.7</v>
@@ -8913,37 +8913,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M93">
-        <v>27.2943216</v>
+        <v>27.5942592</v>
       </c>
       <c r="N93">
-        <v>-17.8343216</v>
+        <v>-18.1342592</v>
       </c>
       <c r="O93">
-        <v>-4.458580400000001</v>
+        <v>-4.5335648</v>
       </c>
       <c r="P93">
-        <v>-13.3757412</v>
+        <v>-13.6006944</v>
       </c>
       <c r="Q93">
-        <v>-6.585741200000002</v>
+        <v>-6.810694399999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.202352908396004</v>
+        <v>1.346922021945505</v>
       </c>
       <c r="T93">
-        <v>7.073333614583396</v>
+        <v>7.957500316406322</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08664805942639732</v>
+        <v>0.08570623269350171</v>
       </c>
       <c r="W93">
-        <v>0.2153683875872555</v>
+        <v>0.2155904703308723</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3465922377055892</v>
+        <v>0.3428249307740068</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3060969944600428</v>
+        <v>0.3079969944600429</v>
       </c>
       <c r="C94">
-        <v>-45.99920496583417</v>
+        <v>-47.59964927444366</v>
       </c>
       <c r="D94">
-        <v>45.32479503416584</v>
+        <v>44.99635072555635</v>
       </c>
       <c r="E94">
-        <v>105.024</v>
+        <v>106.296</v>
       </c>
       <c r="F94">
-        <v>117.024</v>
+        <v>118.296</v>
       </c>
       <c r="G94">
         <v>25.7</v>
@@ -8995,37 +8995,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M94">
-        <v>27.5942592</v>
+        <v>27.8941968</v>
       </c>
       <c r="N94">
-        <v>-18.1342592</v>
+        <v>-18.4341968</v>
       </c>
       <c r="O94">
-        <v>-4.5335648</v>
+        <v>-4.608549200000001</v>
       </c>
       <c r="P94">
-        <v>-13.6006944</v>
+        <v>-13.8256476</v>
       </c>
       <c r="Q94">
-        <v>-6.810694399999998</v>
+        <v>-7.035647600000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.346922021945505</v>
+        <v>1.532796596509148</v>
       </c>
       <c r="T94">
-        <v>7.957500316406322</v>
+        <v>9.09428607589294</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08570623269350171</v>
+        <v>0.08478466029894792</v>
       </c>
       <c r="W94">
-        <v>0.2155904703308723</v>
+        <v>0.2158077771015081</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3428249307740068</v>
+        <v>0.3391386411957916</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3079969944600429</v>
+        <v>0.3098969944600429</v>
       </c>
       <c r="C95">
-        <v>-47.59964927444366</v>
+        <v>-49.19536771188122</v>
       </c>
       <c r="D95">
-        <v>44.99635072555635</v>
+        <v>44.6726322881188</v>
       </c>
       <c r="E95">
-        <v>106.296</v>
+        <v>107.568</v>
       </c>
       <c r="F95">
-        <v>118.296</v>
+        <v>119.568</v>
       </c>
       <c r="G95">
         <v>25.7</v>
@@ -9077,37 +9077,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M95">
-        <v>27.8941968</v>
+        <v>28.1941344</v>
       </c>
       <c r="N95">
-        <v>-18.4341968</v>
+        <v>-18.7341344</v>
       </c>
       <c r="O95">
-        <v>-4.608549200000001</v>
+        <v>-4.683533600000001</v>
       </c>
       <c r="P95">
-        <v>-13.8256476</v>
+        <v>-14.0506008</v>
       </c>
       <c r="Q95">
-        <v>-7.035647600000002</v>
+        <v>-7.260600800000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.532796596509148</v>
+        <v>1.780629362594007</v>
       </c>
       <c r="T95">
-        <v>9.09428607589294</v>
+        <v>10.6100004218751</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08478466029894792</v>
+        <v>0.08388269582768251</v>
       </c>
       <c r="W95">
-        <v>0.2158077771015081</v>
+        <v>0.2160204603238325</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3391386411957916</v>
+        <v>0.3355307833107301</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3098969944600429</v>
+        <v>0.3117969944600428</v>
       </c>
       <c r="C96">
-        <v>-49.19536771188122</v>
+        <v>-50.78646154795904</v>
       </c>
       <c r="D96">
-        <v>44.6726322881188</v>
+        <v>44.35353845204098</v>
       </c>
       <c r="E96">
-        <v>107.568</v>
+        <v>108.84</v>
       </c>
       <c r="F96">
-        <v>119.568</v>
+        <v>120.84</v>
       </c>
       <c r="G96">
         <v>25.7</v>
@@ -9159,37 +9159,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M96">
-        <v>28.1941344</v>
+        <v>28.49407200000001</v>
       </c>
       <c r="N96">
-        <v>-18.7341344</v>
+        <v>-19.03407200000001</v>
       </c>
       <c r="O96">
-        <v>-4.683533600000001</v>
+        <v>-4.758518000000001</v>
       </c>
       <c r="P96">
-        <v>-14.0506008</v>
+        <v>-14.275554</v>
       </c>
       <c r="Q96">
-        <v>-7.260600800000002</v>
+        <v>-7.485554000000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.780629362594007</v>
+        <v>2.12759523511281</v>
       </c>
       <c r="T96">
-        <v>10.6100004218751</v>
+        <v>12.73200050625013</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08388269582768251</v>
+        <v>0.08299972008212794</v>
       </c>
       <c r="W96">
-        <v>0.2160204603238325</v>
+        <v>0.2162286660046342</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3355307833107301</v>
+        <v>0.3319988803285118</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3117969944600428</v>
+        <v>0.3136969944600428</v>
       </c>
       <c r="C97">
-        <v>-50.78646154795904</v>
+        <v>-52.37302917955463</v>
       </c>
       <c r="D97">
-        <v>44.35353845204098</v>
+        <v>44.03897082044537</v>
       </c>
       <c r="E97">
-        <v>108.84</v>
+        <v>110.112</v>
       </c>
       <c r="F97">
-        <v>120.84</v>
+        <v>122.112</v>
       </c>
       <c r="G97">
         <v>25.7</v>
@@ -9241,37 +9241,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M97">
-        <v>28.49407200000001</v>
+        <v>28.7940096</v>
       </c>
       <c r="N97">
-        <v>-19.03407200000001</v>
+        <v>-19.3340096</v>
       </c>
       <c r="O97">
-        <v>-4.758518000000001</v>
+        <v>-4.8335024</v>
       </c>
       <c r="P97">
-        <v>-14.275554</v>
+        <v>-14.5005072</v>
       </c>
       <c r="Q97">
-        <v>-7.485554000000003</v>
+        <v>-7.710507200000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.12759523511281</v>
+        <v>2.648044043891013</v>
       </c>
       <c r="T97">
-        <v>12.73200050625013</v>
+        <v>15.91500063281266</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08299972008212794</v>
+        <v>0.0821351396646058</v>
       </c>
       <c r="W97">
-        <v>0.2162286660046342</v>
+        <v>0.216432534067086</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3319988803285118</v>
+        <v>0.3285405586584231</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3136969944600428</v>
+        <v>0.3155969944600429</v>
       </c>
       <c r="C98">
-        <v>-52.37302917955462</v>
+        <v>-53.95516623177164</v>
       </c>
       <c r="D98">
-        <v>44.03897082044537</v>
+        <v>43.72883376822836</v>
       </c>
       <c r="E98">
-        <v>110.112</v>
+        <v>111.384</v>
       </c>
       <c r="F98">
-        <v>122.112</v>
+        <v>123.384</v>
       </c>
       <c r="G98">
         <v>25.7</v>
@@ -9323,37 +9323,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M98">
-        <v>28.7940096</v>
+        <v>29.0939472</v>
       </c>
       <c r="N98">
-        <v>-19.3340096</v>
+        <v>-19.6339472</v>
       </c>
       <c r="O98">
-        <v>-4.8335024</v>
+        <v>-4.9084868</v>
       </c>
       <c r="P98">
-        <v>-14.5005072</v>
+        <v>-14.7254604</v>
       </c>
       <c r="Q98">
-        <v>-7.710507199999998</v>
+        <v>-7.935460400000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.648044043891006</v>
+        <v>3.515458725188008</v>
       </c>
       <c r="T98">
-        <v>15.91500063281262</v>
+        <v>21.22000084375016</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08213513966460581</v>
+        <v>0.08128838564744491</v>
       </c>
       <c r="W98">
-        <v>0.216432534067086</v>
+        <v>0.2166321986643325</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3285405586584232</v>
+        <v>0.3251535425897797</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3155969944600429</v>
+        <v>0.3174969944600428</v>
       </c>
       <c r="C99">
-        <v>-53.95516623177164</v>
+        <v>-55.532965654856</v>
       </c>
       <c r="D99">
-        <v>43.72883376822836</v>
+        <v>43.42303434514401</v>
       </c>
       <c r="E99">
-        <v>111.384</v>
+        <v>112.656</v>
       </c>
       <c r="F99">
-        <v>123.384</v>
+        <v>124.656</v>
       </c>
       <c r="G99">
         <v>25.7</v>
@@ -9405,37 +9405,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M99">
-        <v>29.0939472</v>
+        <v>29.3938848</v>
       </c>
       <c r="N99">
-        <v>-19.6339472</v>
+        <v>-19.9338848</v>
       </c>
       <c r="O99">
-        <v>-4.9084868</v>
+        <v>-4.9834712</v>
       </c>
       <c r="P99">
-        <v>-14.7254604</v>
+        <v>-14.9504136</v>
       </c>
       <c r="Q99">
-        <v>-7.935460400000001</v>
+        <v>-8.160413600000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.515458725188008</v>
+        <v>5.250288087782011</v>
       </c>
       <c r="T99">
-        <v>21.22000084375016</v>
+        <v>31.83000126562525</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08128838564744491</v>
+        <v>0.0804589123245118</v>
       </c>
       <c r="W99">
-        <v>0.2166321986643325</v>
+        <v>0.2168277884738801</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3251535425897797</v>
+        <v>0.3218356492980472</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3174969944600428</v>
+        <v>0.3193969944600429</v>
       </c>
       <c r="C100">
-        <v>-55.532965654856</v>
+        <v>-57.10651781707401</v>
       </c>
       <c r="D100">
-        <v>43.42303434514401</v>
+        <v>43.12148218292599</v>
       </c>
       <c r="E100">
-        <v>112.656</v>
+        <v>113.928</v>
       </c>
       <c r="F100">
-        <v>124.656</v>
+        <v>125.928</v>
       </c>
       <c r="G100">
         <v>25.7</v>
@@ -9487,37 +9487,37 @@
         <v>9.460000000000001</v>
       </c>
       <c r="M100">
-        <v>29.3938848</v>
+        <v>29.6938224</v>
       </c>
       <c r="N100">
-        <v>-19.9338848</v>
+        <v>-20.2338224</v>
       </c>
       <c r="O100">
-        <v>-4.9834712</v>
+        <v>-5.0584556</v>
       </c>
       <c r="P100">
-        <v>-14.9504136</v>
+        <v>-15.1753668</v>
       </c>
       <c r="Q100">
-        <v>-8.160413600000002</v>
+        <v>-8.3853668</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.250288087782011</v>
+        <v>10.45477617556402</v>
       </c>
       <c r="T100">
-        <v>31.83000126562525</v>
+        <v>63.66000253125049</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0804589123245118</v>
+        <v>0.07964619603840561</v>
       </c>
       <c r="W100">
-        <v>0.2168277884738801</v>
+        <v>0.217019426974144</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3218356492980472</v>
+        <v>0.3185847841536225</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3193969944600429</v>
-      </c>
-      <c r="C101">
-        <v>-57.10651781707401</v>
-      </c>
-      <c r="D101">
-        <v>43.12148218292599</v>
-      </c>
-      <c r="E101">
-        <v>113.928</v>
-      </c>
-      <c r="F101">
-        <v>125.928</v>
-      </c>
-      <c r="G101">
-        <v>25.7</v>
-      </c>
-      <c r="H101">
-        <v>115.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.25</v>
-      </c>
-      <c r="K101">
-        <v>6.79</v>
-      </c>
-      <c r="L101">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="M101">
-        <v>29.6938224</v>
-      </c>
-      <c r="N101">
-        <v>-20.2338224</v>
-      </c>
-      <c r="O101">
-        <v>-5.0584556</v>
-      </c>
-      <c r="P101">
-        <v>-15.1753668</v>
-      </c>
-      <c r="Q101">
-        <v>-8.3853668</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.45477617556402</v>
-      </c>
-      <c r="T101">
-        <v>63.66000253125049</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07964619603840561</v>
-      </c>
-      <c r="W101">
-        <v>0.217019426974144</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3185847841536225</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
